--- a/ssqbz.xlsx
+++ b/ssqbz.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P624"/>
+  <dimension ref="A1:Q624"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="16"/>
   <cols>
     <col width="8.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -618,6 +618,9 @@
       <c r="P1" t="n">
         <v>128</v>
       </c>
+      <c r="Q1" t="n">
+        <v>360230056</v>
+      </c>
     </row>
     <row r="2" ht="19" customHeight="1">
       <c r="A2" s="1" t="n">
@@ -669,6 +672,9 @@
       </c>
       <c r="P2" t="n">
         <v>180</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>357972850</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
@@ -723,6 +729,9 @@
       </c>
       <c r="P3" t="n">
         <v>127</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>337463590</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
@@ -772,6 +781,9 @@
       <c r="P4" t="n">
         <v>141</v>
       </c>
+      <c r="Q4" t="n">
+        <v>363371278</v>
+      </c>
     </row>
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="1" t="n">
@@ -826,6 +838,9 @@
       <c r="P5" t="n">
         <v>114</v>
       </c>
+      <c r="Q5" t="n">
+        <v>389679034</v>
+      </c>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="1" t="n">
@@ -882,6 +897,9 @@
       <c r="P6" t="n">
         <v>61</v>
       </c>
+      <c r="Q6" t="n">
+        <v>359187786</v>
+      </c>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="1" t="n">
@@ -934,6 +952,9 @@
       <c r="P7" t="n">
         <v>81</v>
       </c>
+      <c r="Q7" t="n">
+        <v>356510652</v>
+      </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="1" t="n">
@@ -995,6 +1016,9 @@
       </c>
       <c r="P8" t="n">
         <v>92</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>391678014</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
@@ -1042,6 +1066,9 @@
       <c r="P9" t="n">
         <v>77</v>
       </c>
+      <c r="Q9" t="n">
+        <v>350153658</v>
+      </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="1" t="n">
@@ -1094,6 +1121,9 @@
       <c r="P10" t="n">
         <v>162</v>
       </c>
+      <c r="Q10" t="n">
+        <v>352329270</v>
+      </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="1" t="n">
@@ -1146,6 +1176,9 @@
       <c r="P11" t="n">
         <v>78</v>
       </c>
+      <c r="Q11" t="n">
+        <v>378857894</v>
+      </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="1" t="n">
@@ -1206,6 +1239,9 @@
       <c r="P12" t="n">
         <v>126</v>
       </c>
+      <c r="Q12" t="n">
+        <v>336926030</v>
+      </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="1" t="n">
@@ -1268,6 +1304,9 @@
       <c r="P13" t="n">
         <v>216</v>
       </c>
+      <c r="Q13" t="n">
+        <v>340378840</v>
+      </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="1" t="n">
@@ -1330,6 +1369,9 @@
       <c r="P14" t="n">
         <v>80</v>
       </c>
+      <c r="Q14" t="n">
+        <v>361140396</v>
+      </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="1" t="n">
@@ -1384,6 +1426,9 @@
       <c r="P15" t="n">
         <v>64</v>
       </c>
+      <c r="Q15" t="n">
+        <v>331252342</v>
+      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="1" t="n">
@@ -1445,6 +1490,9 @@
       </c>
       <c r="P16" t="n">
         <v>69</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>329515310</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
@@ -1494,6 +1542,9 @@
       <c r="P17" t="n">
         <v>181</v>
       </c>
+      <c r="Q17" t="n">
+        <v>360023818</v>
+      </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="1" t="n">
@@ -1548,6 +1599,9 @@
       <c r="P18" t="n">
         <v>81</v>
       </c>
+      <c r="Q18" t="n">
+        <v>340689068</v>
+      </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="1" t="n">
@@ -1600,6 +1654,9 @@
       <c r="P19" t="n">
         <v>143</v>
       </c>
+      <c r="Q19" t="n">
+        <v>348395414</v>
+      </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="1" t="n">
@@ -1651,6 +1708,9 @@
       </c>
       <c r="P20" t="n">
         <v>281</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>370987262</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -1699,6 +1759,9 @@
       </c>
       <c r="P21" t="n">
         <v>147</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>347891686</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
@@ -1746,6 +1809,9 @@
       <c r="P22" t="n">
         <v>170</v>
       </c>
+      <c r="Q22" t="n">
+        <v>354071622</v>
+      </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="1" t="n">
@@ -1807,6 +1873,9 @@
       </c>
       <c r="P23" t="n">
         <v>216</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>380359658</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
@@ -1859,6 +1928,9 @@
       </c>
       <c r="P24" t="n">
         <v>226</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>356598990</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -1906,6 +1978,9 @@
       <c r="P25" t="n">
         <v>141</v>
       </c>
+      <c r="Q25" t="n">
+        <v>354289328</v>
+      </c>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="1" t="n">
@@ -1968,6 +2043,9 @@
       <c r="P26" t="n">
         <v>95</v>
       </c>
+      <c r="Q26" t="n">
+        <v>385506202</v>
+      </c>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="1" t="n">
@@ -2030,6 +2108,9 @@
       <c r="P27" t="n">
         <v>141</v>
       </c>
+      <c r="Q27" t="n">
+        <v>352213628</v>
+      </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="1" t="n">
@@ -2083,6 +2164,9 @@
       </c>
       <c r="P28" t="n">
         <v>131</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>354915638</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
@@ -2132,6 +2216,9 @@
       <c r="P29" t="n">
         <v>78</v>
       </c>
+      <c r="Q29" t="n">
+        <v>379959636</v>
+      </c>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="1" t="n">
@@ -2188,6 +2275,9 @@
       <c r="P30" t="n">
         <v>142</v>
       </c>
+      <c r="Q30" t="n">
+        <v>342718328</v>
+      </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="1" t="n">
@@ -2244,6 +2334,9 @@
       <c r="P31" t="n">
         <v>186</v>
       </c>
+      <c r="Q31" t="n">
+        <v>345118818</v>
+      </c>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="1" t="n">
@@ -2303,6 +2396,9 @@
       </c>
       <c r="P32" t="n">
         <v>69</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>366650644</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
@@ -2358,6 +2454,9 @@
       <c r="P33" t="n">
         <v>68</v>
       </c>
+      <c r="Q33" t="n">
+        <v>341273762</v>
+      </c>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="1" t="n">
@@ -2420,6 +2519,9 @@
       <c r="P34" t="n">
         <v>129</v>
       </c>
+      <c r="Q34" t="n">
+        <v>342797508</v>
+      </c>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="1" t="n">
@@ -2472,6 +2574,9 @@
       <c r="P35" t="n">
         <v>186</v>
       </c>
+      <c r="Q35" t="n">
+        <v>373064250</v>
+      </c>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="1" t="n">
@@ -2533,6 +2638,9 @@
       </c>
       <c r="P36" t="n">
         <v>79</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>347371994</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
@@ -2582,6 +2690,9 @@
       <c r="P37" t="n">
         <v>258</v>
       </c>
+      <c r="Q37" t="n">
+        <v>347550570</v>
+      </c>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="1" t="n">
@@ -2637,6 +2748,9 @@
       </c>
       <c r="P38" t="n">
         <v>97</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>368808592</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
@@ -2690,6 +2804,9 @@
       <c r="P39" t="n">
         <v>112</v>
       </c>
+      <c r="Q39" t="n">
+        <v>341538762</v>
+      </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="1" t="n">
@@ -2746,6 +2863,9 @@
       <c r="P40" t="n">
         <v>61</v>
       </c>
+      <c r="Q40" t="n">
+        <v>345421240</v>
+      </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="1" t="n">
@@ -2805,6 +2925,9 @@
       </c>
       <c r="P41" t="n">
         <v>129</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>370042706</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
@@ -2850,6 +2973,9 @@
       <c r="P42" t="n">
         <v>168</v>
       </c>
+      <c r="Q42" t="n">
+        <v>340253450</v>
+      </c>
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="1" t="n">
@@ -2894,6 +3020,9 @@
       <c r="P43" t="n">
         <v>90</v>
       </c>
+      <c r="Q43" t="n">
+        <v>342434670</v>
+      </c>
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="1" t="n">
@@ -2945,6 +3074,9 @@
       </c>
       <c r="P44" t="n">
         <v>98</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>365943774</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
@@ -2994,6 +3126,9 @@
       <c r="P45" t="n">
         <v>244</v>
       </c>
+      <c r="Q45" t="n">
+        <v>335981918</v>
+      </c>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="1" t="n">
@@ -3054,6 +3189,9 @@
       <c r="P46" t="n">
         <v>245</v>
       </c>
+      <c r="Q46" t="n">
+        <v>337222664</v>
+      </c>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="1" t="n">
@@ -3113,6 +3251,9 @@
       </c>
       <c r="P47" t="n">
         <v>58</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>363673578</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
@@ -3162,6 +3303,9 @@
       <c r="P48" t="n">
         <v>186</v>
       </c>
+      <c r="Q48" t="n">
+        <v>333751422</v>
+      </c>
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="1" t="n">
@@ -3222,6 +3366,9 @@
       <c r="P49" t="n">
         <v>71</v>
       </c>
+      <c r="Q49" t="n">
+        <v>339954958</v>
+      </c>
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="1" t="n">
@@ -3278,6 +3425,9 @@
       <c r="P50" t="n">
         <v>94</v>
       </c>
+      <c r="Q50" t="n">
+        <v>374401638</v>
+      </c>
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="1" t="n">
@@ -3334,6 +3484,9 @@
       <c r="P51" t="n">
         <v>65</v>
       </c>
+      <c r="Q51" t="n">
+        <v>339168020</v>
+      </c>
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="1" t="n">
@@ -3394,6 +3547,9 @@
       <c r="P52" t="n">
         <v>34</v>
       </c>
+      <c r="Q52" t="n">
+        <v>339839938</v>
+      </c>
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="1" t="n">
@@ -3449,6 +3605,9 @@
       </c>
       <c r="P53" t="n">
         <v>256</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>368635154</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
@@ -3498,6 +3657,9 @@
       <c r="P54" t="n">
         <v>106</v>
       </c>
+      <c r="Q54" t="n">
+        <v>338953236</v>
+      </c>
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="1" t="n">
@@ -3554,6 +3716,9 @@
       <c r="P55" t="n">
         <v>134</v>
       </c>
+      <c r="Q55" t="n">
+        <v>342584116</v>
+      </c>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="1" t="n">
@@ -3613,6 +3778,9 @@
       </c>
       <c r="P56" t="n">
         <v>137</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>360805992</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
@@ -3660,6 +3828,9 @@
       <c r="P57" t="n">
         <v>146</v>
       </c>
+      <c r="Q57" t="n">
+        <v>331343836</v>
+      </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="1" t="n">
@@ -3716,6 +3887,9 @@
       <c r="P58" t="n">
         <v>214</v>
       </c>
+      <c r="Q58" t="n">
+        <v>337087306</v>
+      </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="1" t="n">
@@ -3771,6 +3945,9 @@
       </c>
       <c r="P59" t="n">
         <v>85</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>357410590</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
@@ -3823,6 +4000,9 @@
       </c>
       <c r="P60" t="n">
         <v>50</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>336123528</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
@@ -3872,6 +4052,9 @@
       <c r="P61" t="n">
         <v>139</v>
       </c>
+      <c r="Q61" t="n">
+        <v>342747048</v>
+      </c>
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="1" t="n">
@@ -3928,6 +4111,9 @@
       <c r="P62" t="n">
         <v>269</v>
       </c>
+      <c r="Q62" t="n">
+        <v>379260702</v>
+      </c>
     </row>
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="1" t="n">
@@ -3980,6 +4166,9 @@
       <c r="P63" t="n">
         <v>78</v>
       </c>
+      <c r="Q63" t="n">
+        <v>349805376</v>
+      </c>
     </row>
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="1" t="n">
@@ -4032,6 +4221,9 @@
       <c r="P64" t="n">
         <v>237</v>
       </c>
+      <c r="Q64" t="n">
+        <v>352346658</v>
+      </c>
     </row>
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="1" t="n">
@@ -4094,6 +4286,9 @@
       <c r="P65" t="n">
         <v>160</v>
       </c>
+      <c r="Q65" t="n">
+        <v>385923798</v>
+      </c>
     </row>
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="1" t="n">
@@ -4146,6 +4341,9 @@
       <c r="P66" t="n">
         <v>169</v>
       </c>
+      <c r="Q66" t="n">
+        <v>348893862</v>
+      </c>
     </row>
     <row r="67" ht="19" customHeight="1">
       <c r="A67" s="1" t="n">
@@ -4202,6 +4400,9 @@
       <c r="P67" t="n">
         <v>84</v>
       </c>
+      <c r="Q67" t="n">
+        <v>363604180</v>
+      </c>
     </row>
     <row r="68" ht="19" customHeight="1">
       <c r="A68" s="1" t="n">
@@ -4254,6 +4455,9 @@
       <c r="P68" t="n">
         <v>241</v>
       </c>
+      <c r="Q68" t="n">
+        <v>347069064</v>
+      </c>
     </row>
     <row r="69" ht="19" customHeight="1">
       <c r="A69" s="1" t="n">
@@ -4313,6 +4517,9 @@
       </c>
       <c r="P69" t="n">
         <v>169</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>359461828</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
@@ -4366,6 +4573,9 @@
       <c r="P70" t="n">
         <v>93</v>
       </c>
+      <c r="Q70" t="n">
+        <v>337975208</v>
+      </c>
     </row>
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="1" t="n">
@@ -4421,6 +4631,9 @@
       </c>
       <c r="P71" t="n">
         <v>166</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>345578024</v>
       </c>
     </row>
     <row r="72" ht="19" customHeight="1">
@@ -4470,6 +4683,9 @@
       <c r="P72" t="n">
         <v>173</v>
       </c>
+      <c r="Q72" t="n">
+        <v>374309728</v>
+      </c>
     </row>
     <row r="73" ht="19" customHeight="1">
       <c r="A73" s="1" t="n">
@@ -4530,6 +4746,9 @@
       <c r="P73" t="n">
         <v>309</v>
       </c>
+      <c r="Q73" t="n">
+        <v>341495720</v>
+      </c>
     </row>
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="1" t="n">
@@ -4592,6 +4811,9 @@
       <c r="P74" t="n">
         <v>288</v>
       </c>
+      <c r="Q74" t="n">
+        <v>355500194</v>
+      </c>
     </row>
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="1" t="n">
@@ -4652,6 +4874,9 @@
       <c r="P75" t="n">
         <v>102</v>
       </c>
+      <c r="Q75" t="n">
+        <v>380066114</v>
+      </c>
     </row>
     <row r="76" ht="19" customHeight="1">
       <c r="A76" s="1" t="n">
@@ -4704,6 +4929,9 @@
       <c r="P76" t="n">
         <v>214</v>
       </c>
+      <c r="Q76" t="n">
+        <v>350001646</v>
+      </c>
     </row>
     <row r="77" ht="19" customHeight="1">
       <c r="A77" s="1" t="n">
@@ -4759,6 +4987,9 @@
       </c>
       <c r="P77" t="n">
         <v>637</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>360850820</v>
       </c>
     </row>
     <row r="78" ht="19" customHeight="1">
@@ -4806,6 +5037,9 @@
       <c r="P78" t="n">
         <v>124</v>
       </c>
+      <c r="Q78" t="n">
+        <v>383396494</v>
+      </c>
     </row>
     <row r="79" ht="19" customHeight="1">
       <c r="A79" s="1" t="n">
@@ -4861,6 +5095,9 @@
       </c>
       <c r="P79" t="n">
         <v>231</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>429659904</v>
       </c>
     </row>
     <row r="80" ht="19" customHeight="1">
@@ -4910,6 +5147,9 @@
       <c r="P80" t="n">
         <v>151</v>
       </c>
+      <c r="Q80" t="n">
+        <v>436137344</v>
+      </c>
     </row>
     <row r="81" ht="19" customHeight="1">
       <c r="A81" s="1" t="n">
@@ -4969,6 +5209,9 @@
       </c>
       <c r="P81" t="n">
         <v>178</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>455409958</v>
       </c>
     </row>
     <row r="82" ht="19" customHeight="1">
@@ -5016,6 +5259,9 @@
       <c r="P82" t="n">
         <v>210</v>
       </c>
+      <c r="Q82" t="n">
+        <v>420999886</v>
+      </c>
     </row>
     <row r="83" ht="19" customHeight="1">
       <c r="A83" s="1" t="n">
@@ -5069,6 +5315,9 @@
       </c>
       <c r="P83" t="n">
         <v>102</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>430007836</v>
       </c>
     </row>
     <row r="84" ht="19" customHeight="1">
@@ -5118,6 +5367,9 @@
       <c r="P84" t="n">
         <v>542</v>
       </c>
+      <c r="Q84" t="n">
+        <v>446023212</v>
+      </c>
     </row>
     <row r="85" ht="19" customHeight="1">
       <c r="A85" s="1" t="n">
@@ -5166,6 +5418,9 @@
       <c r="P85" t="n">
         <v>251</v>
       </c>
+      <c r="Q85" t="n">
+        <v>425292626</v>
+      </c>
     </row>
     <row r="86" ht="19" customHeight="1">
       <c r="A86" s="1" t="n">
@@ -5226,6 +5481,9 @@
       <c r="P86" t="n">
         <v>88</v>
       </c>
+      <c r="Q86" t="n">
+        <v>439981994</v>
+      </c>
     </row>
     <row r="87" ht="19" customHeight="1">
       <c r="A87" s="1" t="n">
@@ -5282,6 +5540,9 @@
       <c r="P87" t="n">
         <v>241</v>
       </c>
+      <c r="Q87" t="n">
+        <v>457083562</v>
+      </c>
     </row>
     <row r="88" ht="19" customHeight="1">
       <c r="A88" s="1" t="n">
@@ -5335,6 +5596,9 @@
       </c>
       <c r="P88" t="n">
         <v>90</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>404859714</v>
       </c>
     </row>
     <row r="89" ht="19" customHeight="1">
@@ -5380,6 +5644,9 @@
       <c r="P89" t="n">
         <v>143</v>
       </c>
+      <c r="Q89" t="n">
+        <v>402652460</v>
+      </c>
     </row>
     <row r="90" ht="19" customHeight="1">
       <c r="A90" s="1" t="n">
@@ -5436,6 +5703,9 @@
       <c r="P90" t="n">
         <v>122</v>
       </c>
+      <c r="Q90" t="n">
+        <v>412826960</v>
+      </c>
     </row>
     <row r="91" ht="19" customHeight="1">
       <c r="A91" s="1" t="n">
@@ -5495,6 +5765,9 @@
       </c>
       <c r="P91" t="n">
         <v>160</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>380398430</v>
       </c>
     </row>
     <row r="92" ht="19" customHeight="1">
@@ -5542,6 +5815,9 @@
       <c r="P92" t="n">
         <v>67</v>
       </c>
+      <c r="Q92" t="n">
+        <v>382295872</v>
+      </c>
     </row>
     <row r="93" ht="19" customHeight="1">
       <c r="A93" s="1" t="n">
@@ -5602,6 +5878,9 @@
       <c r="P93" t="n">
         <v>443</v>
       </c>
+      <c r="Q93" t="n">
+        <v>421220444</v>
+      </c>
     </row>
     <row r="94" ht="19" customHeight="1">
       <c r="A94" s="1" t="n">
@@ -5664,6 +5943,9 @@
       <c r="P94" t="n">
         <v>673</v>
       </c>
+      <c r="Q94" t="n">
+        <v>397499610</v>
+      </c>
     </row>
     <row r="95" ht="19" customHeight="1">
       <c r="A95" s="1" t="n">
@@ -5726,6 +6008,9 @@
       <c r="P95" t="n">
         <v>135</v>
       </c>
+      <c r="Q95" t="n">
+        <v>415110854</v>
+      </c>
     </row>
     <row r="96" ht="19" customHeight="1">
       <c r="A96" s="1" t="n">
@@ -5780,6 +6065,9 @@
       <c r="P96" t="n">
         <v>122</v>
       </c>
+      <c r="Q96" t="n">
+        <v>440572602</v>
+      </c>
     </row>
     <row r="97" ht="19" customHeight="1">
       <c r="A97" s="1" t="n">
@@ -5840,6 +6128,9 @@
       <c r="P97" t="n">
         <v>149</v>
       </c>
+      <c r="Q97" t="n">
+        <v>397641696</v>
+      </c>
     </row>
     <row r="98" ht="19" customHeight="1">
       <c r="A98" s="1" t="n">
@@ -5900,6 +6191,9 @@
       <c r="P98" t="n">
         <v>65</v>
       </c>
+      <c r="Q98" t="n">
+        <v>400859910</v>
+      </c>
     </row>
     <row r="99" ht="19" customHeight="1">
       <c r="A99" s="1" t="n">
@@ -5960,6 +6254,9 @@
       <c r="P99" t="n">
         <v>68</v>
       </c>
+      <c r="Q99" t="n">
+        <v>366333090</v>
+      </c>
     </row>
     <row r="100" ht="19" customHeight="1">
       <c r="A100" s="1" t="n">
@@ -6020,6 +6317,9 @@
       <c r="P100" t="n">
         <v>391</v>
       </c>
+      <c r="Q100" t="n">
+        <v>319241960</v>
+      </c>
     </row>
     <row r="101" ht="19" customHeight="1">
       <c r="A101" s="1" t="n">
@@ -6082,6 +6382,9 @@
       <c r="P101" t="n">
         <v>148</v>
       </c>
+      <c r="Q101" t="n">
+        <v>308727648</v>
+      </c>
     </row>
     <row r="102" ht="19" customHeight="1">
       <c r="A102" s="1" t="n">
@@ -6142,6 +6445,9 @@
       <c r="P102" t="n">
         <v>72</v>
       </c>
+      <c r="Q102" t="n">
+        <v>328466772</v>
+      </c>
     </row>
     <row r="103" ht="19" customHeight="1">
       <c r="A103" s="1" t="n">
@@ -6202,6 +6508,9 @@
       <c r="P103" t="n">
         <v>94</v>
       </c>
+      <c r="Q103" t="n">
+        <v>305443962</v>
+      </c>
     </row>
     <row r="104" ht="19" customHeight="1">
       <c r="A104" s="1" t="n">
@@ -6262,6 +6571,9 @@
       <c r="P104" t="n">
         <v>203</v>
       </c>
+      <c r="Q104" t="n">
+        <v>322732470</v>
+      </c>
     </row>
     <row r="105" ht="19" customHeight="1">
       <c r="A105" s="1" t="n">
@@ -6316,6 +6628,9 @@
       <c r="P105" t="n">
         <v>135</v>
       </c>
+      <c r="Q105" t="n">
+        <v>349018800</v>
+      </c>
     </row>
     <row r="106" ht="19" customHeight="1">
       <c r="A106" s="1" t="n">
@@ -6370,6 +6685,9 @@
       <c r="P106" t="n">
         <v>164</v>
       </c>
+      <c r="Q106" t="n">
+        <v>317440920</v>
+      </c>
     </row>
     <row r="107" ht="19" customHeight="1">
       <c r="A107" s="1" t="n">
@@ -6422,6 +6740,9 @@
       <c r="P107" t="n">
         <v>112</v>
       </c>
+      <c r="Q107" t="n">
+        <v>332514694</v>
+      </c>
     </row>
     <row r="108" ht="19" customHeight="1">
       <c r="A108" s="1" t="n">
@@ -6481,6 +6802,9 @@
       </c>
       <c r="P108" t="n">
         <v>166</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>362777504</v>
       </c>
     </row>
     <row r="109" ht="19" customHeight="1">
@@ -6530,6 +6854,9 @@
       <c r="P109" t="n">
         <v>153</v>
       </c>
+      <c r="Q109" t="n">
+        <v>331127174</v>
+      </c>
     </row>
     <row r="110" ht="19" customHeight="1">
       <c r="A110" s="1" t="n">
@@ -6584,6 +6911,9 @@
       <c r="P110" t="n">
         <v>109</v>
       </c>
+      <c r="Q110" t="n">
+        <v>341187596</v>
+      </c>
     </row>
     <row r="111" ht="19" customHeight="1">
       <c r="A111" s="1" t="n">
@@ -6640,6 +6970,9 @@
       <c r="P111" t="n">
         <v>160</v>
       </c>
+      <c r="Q111" t="n">
+        <v>357680590</v>
+      </c>
     </row>
     <row r="112" ht="19" customHeight="1">
       <c r="A112" s="1" t="n">
@@ -6692,6 +7025,9 @@
       <c r="P112" t="n">
         <v>146</v>
       </c>
+      <c r="Q112" t="n">
+        <v>367864780</v>
+      </c>
     </row>
     <row r="113" ht="19" customHeight="1">
       <c r="A113" s="1" t="n">
@@ -6747,6 +7083,9 @@
       </c>
       <c r="P113" t="n">
         <v>225</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>370445322</v>
       </c>
     </row>
     <row r="114" ht="19" customHeight="1">
@@ -6800,6 +7139,9 @@
       <c r="P114" t="n">
         <v>220</v>
       </c>
+      <c r="Q114" t="n">
+        <v>335698884</v>
+      </c>
     </row>
     <row r="115" ht="19" customHeight="1">
       <c r="A115" s="1" t="n">
@@ -6855,6 +7197,9 @@
       </c>
       <c r="P115" t="n">
         <v>252</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>344777252</v>
       </c>
     </row>
     <row r="116" ht="19" customHeight="1">
@@ -6910,6 +7255,9 @@
       <c r="P116" t="n">
         <v>270</v>
       </c>
+      <c r="Q116" t="n">
+        <v>377681908</v>
+      </c>
     </row>
     <row r="117" ht="19" customHeight="1">
       <c r="A117" s="1" t="n">
@@ -6970,6 +7318,9 @@
       <c r="P117" t="n">
         <v>81</v>
       </c>
+      <c r="Q117" t="n">
+        <v>351959204</v>
+      </c>
     </row>
     <row r="118" ht="19" customHeight="1">
       <c r="A118" s="1" t="n">
@@ -7032,6 +7383,9 @@
       <c r="P118" t="n">
         <v>147</v>
       </c>
+      <c r="Q118" t="n">
+        <v>354854954</v>
+      </c>
     </row>
     <row r="119" ht="19" customHeight="1">
       <c r="A119" s="1" t="n">
@@ -7087,6 +7441,9 @@
       </c>
       <c r="P119" t="n">
         <v>195</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>392727530</v>
       </c>
     </row>
     <row r="120" ht="19" customHeight="1">
@@ -7132,6 +7489,9 @@
       <c r="P120" t="n">
         <v>79</v>
       </c>
+      <c r="Q120" t="n">
+        <v>363237418</v>
+      </c>
     </row>
     <row r="121" ht="19" customHeight="1">
       <c r="A121" s="1" t="n">
@@ -7183,6 +7543,9 @@
       </c>
       <c r="P121" t="n">
         <v>195</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>385010210</v>
       </c>
     </row>
     <row r="122" ht="19" customHeight="1">
@@ -7224,6 +7587,9 @@
       <c r="P122" t="n">
         <v>380</v>
       </c>
+      <c r="Q122" t="n">
+        <v>428078014</v>
+      </c>
     </row>
     <row r="123" ht="19" customHeight="1">
       <c r="A123" s="1" t="n">
@@ -7284,6 +7650,9 @@
       <c r="P123" t="n">
         <v>110</v>
       </c>
+      <c r="Q123" t="n">
+        <v>399695170</v>
+      </c>
     </row>
     <row r="124" ht="19" customHeight="1">
       <c r="A124" s="1" t="n">
@@ -7345,6 +7714,9 @@
       </c>
       <c r="P124" t="n">
         <v>92</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>394774502</v>
       </c>
     </row>
     <row r="125" ht="19" customHeight="1">
@@ -7398,6 +7770,9 @@
       <c r="P125" t="n">
         <v>186</v>
       </c>
+      <c r="Q125" t="n">
+        <v>430229092</v>
+      </c>
     </row>
     <row r="126" ht="19" customHeight="1">
       <c r="A126" s="1" t="n">
@@ -7458,6 +7833,9 @@
       <c r="P126" t="n">
         <v>112</v>
       </c>
+      <c r="Q126" t="n">
+        <v>393991274</v>
+      </c>
     </row>
     <row r="127" ht="19" customHeight="1">
       <c r="A127" s="1" t="n">
@@ -7518,6 +7896,9 @@
       <c r="P127" t="n">
         <v>258</v>
       </c>
+      <c r="Q127" t="n">
+        <v>394377912</v>
+      </c>
     </row>
     <row r="128" ht="19" customHeight="1">
       <c r="A128" s="1" t="n">
@@ -7574,6 +7955,9 @@
       <c r="P128" t="n">
         <v>487</v>
       </c>
+      <c r="Q128" t="n">
+        <v>424465912</v>
+      </c>
     </row>
     <row r="129" ht="19" customHeight="1">
       <c r="A129" s="1" t="n">
@@ -7630,6 +8014,9 @@
       <c r="P129" t="n">
         <v>118</v>
       </c>
+      <c r="Q129" t="n">
+        <v>383537242</v>
+      </c>
     </row>
     <row r="130" ht="19" customHeight="1">
       <c r="A130" s="1" t="n">
@@ -7690,6 +8077,9 @@
       <c r="P130" t="n">
         <v>98</v>
       </c>
+      <c r="Q130" t="n">
+        <v>382398740</v>
+      </c>
     </row>
     <row r="131" ht="19" customHeight="1">
       <c r="A131" s="1" t="n">
@@ -7750,6 +8140,9 @@
       <c r="P131" t="n">
         <v>88</v>
       </c>
+      <c r="Q131" t="n">
+        <v>405939502</v>
+      </c>
     </row>
     <row r="132" ht="19" customHeight="1">
       <c r="A132" s="1" t="n">
@@ -7804,6 +8197,9 @@
       <c r="P132" t="n">
         <v>151</v>
       </c>
+      <c r="Q132" t="n">
+        <v>378131048</v>
+      </c>
     </row>
     <row r="133" ht="19" customHeight="1">
       <c r="A133" s="1" t="n">
@@ -7855,6 +8251,9 @@
       </c>
       <c r="P133" t="n">
         <v>173</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>373970632</v>
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
@@ -7910,6 +8309,9 @@
       <c r="P134" t="n">
         <v>78</v>
       </c>
+      <c r="Q134" t="n">
+        <v>407635670</v>
+      </c>
     </row>
     <row r="135" ht="19" customHeight="1">
       <c r="A135" s="1" t="n">
@@ -7964,6 +8366,9 @@
       <c r="P135" t="n">
         <v>309</v>
       </c>
+      <c r="Q135" t="n">
+        <v>377795536</v>
+      </c>
     </row>
     <row r="136" ht="19" customHeight="1">
       <c r="A136" s="1" t="n">
@@ -8024,6 +8429,9 @@
       <c r="P136" t="n">
         <v>142</v>
       </c>
+      <c r="Q136" t="n">
+        <v>378271328</v>
+      </c>
     </row>
     <row r="137" ht="19" customHeight="1">
       <c r="A137" s="1" t="n">
@@ -8084,6 +8492,9 @@
       <c r="P137" t="n">
         <v>240</v>
       </c>
+      <c r="Q137" t="n">
+        <v>407044870</v>
+      </c>
     </row>
     <row r="138" ht="19" customHeight="1">
       <c r="A138" s="1" t="n">
@@ -8144,6 +8555,9 @@
       <c r="P138" t="n">
         <v>146</v>
       </c>
+      <c r="Q138" t="n">
+        <v>371464196</v>
+      </c>
     </row>
     <row r="139" ht="19" customHeight="1">
       <c r="A139" s="1" t="n">
@@ -8204,6 +8618,9 @@
       <c r="P139" t="n">
         <v>100</v>
       </c>
+      <c r="Q139" t="n">
+        <v>376157550</v>
+      </c>
     </row>
     <row r="140" ht="19" customHeight="1">
       <c r="A140" s="1" t="n">
@@ -8259,6 +8676,9 @@
       </c>
       <c r="P140" t="n">
         <v>271</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>402105258</v>
       </c>
     </row>
     <row r="141" ht="19" customHeight="1">
@@ -8307,6 +8727,9 @@
       </c>
       <c r="P141" t="n">
         <v>115</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>357460864</v>
       </c>
     </row>
     <row r="142" ht="19" customHeight="1">
@@ -8352,6 +8775,9 @@
       <c r="P142" t="n">
         <v>135</v>
       </c>
+      <c r="Q142" t="n">
+        <v>368841578</v>
+      </c>
     </row>
     <row r="143" ht="19" customHeight="1">
       <c r="A143" s="1" t="n">
@@ -8414,6 +8840,9 @@
       <c r="P143" t="n">
         <v>191</v>
       </c>
+      <c r="Q143" t="n">
+        <v>409186858</v>
+      </c>
     </row>
     <row r="144" ht="19" customHeight="1">
       <c r="A144" s="1" t="n">
@@ -8473,6 +8902,9 @@
       </c>
       <c r="P144" t="n">
         <v>165</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>372777348</v>
       </c>
     </row>
     <row r="145" ht="19" customHeight="1">
@@ -8525,6 +8957,9 @@
       </c>
       <c r="P145" t="n">
         <v>118</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>379030400</v>
       </c>
     </row>
     <row r="146" ht="19" customHeight="1">
@@ -8574,6 +9009,9 @@
       <c r="P146" t="n">
         <v>224</v>
       </c>
+      <c r="Q146" t="n">
+        <v>406450374</v>
+      </c>
     </row>
     <row r="147" ht="19" customHeight="1">
       <c r="A147" s="1" t="n">
@@ -8626,6 +9064,9 @@
       <c r="P147" t="n">
         <v>228</v>
       </c>
+      <c r="Q147" t="n">
+        <v>370609676</v>
+      </c>
     </row>
     <row r="148" ht="19" customHeight="1">
       <c r="A148" s="1" t="n">
@@ -8679,6 +9120,9 @@
       </c>
       <c r="P148" t="n">
         <v>99</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>375494004</v>
       </c>
     </row>
     <row r="149" ht="19" customHeight="1">
@@ -8728,6 +9172,9 @@
       <c r="P149" t="n">
         <v>240</v>
       </c>
+      <c r="Q149" t="n">
+        <v>398638950</v>
+      </c>
     </row>
     <row r="150" ht="19" customHeight="1">
       <c r="A150" s="1" t="n">
@@ -8789,6 +9236,9 @@
       </c>
       <c r="P150" t="n">
         <v>121</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>364967218</v>
       </c>
     </row>
     <row r="151" ht="19" customHeight="1">
@@ -8838,6 +9288,9 @@
       <c r="P151" t="n">
         <v>123</v>
       </c>
+      <c r="Q151" t="n">
+        <v>373486114</v>
+      </c>
     </row>
     <row r="152" ht="19" customHeight="1">
       <c r="A152" s="1" t="n">
@@ -8893,6 +9346,9 @@
       </c>
       <c r="P152" t="n">
         <v>158</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>362109840</v>
       </c>
     </row>
     <row r="153" ht="19" customHeight="1">
@@ -8942,6 +9398,9 @@
       <c r="P153" t="n">
         <v>170</v>
       </c>
+      <c r="Q153" t="n">
+        <v>328857030</v>
+      </c>
     </row>
     <row r="154" ht="19" customHeight="1">
       <c r="A154" s="1" t="n">
@@ -9004,6 +9463,9 @@
       <c r="P154" t="n">
         <v>115</v>
       </c>
+      <c r="Q154" t="n">
+        <v>359185180</v>
+      </c>
     </row>
     <row r="155" ht="19" customHeight="1">
       <c r="A155" s="1" t="n">
@@ -9063,6 +9525,9 @@
       </c>
       <c r="P155" t="n">
         <v>95</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>388332454</v>
       </c>
     </row>
     <row r="156" ht="19" customHeight="1">
@@ -9111,6 +9576,9 @@
       </c>
       <c r="P156" t="n">
         <v>179</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>358038114</v>
       </c>
     </row>
     <row r="157" ht="19" customHeight="1">
@@ -9160,6 +9628,9 @@
       <c r="P157" t="n">
         <v>420</v>
       </c>
+      <c r="Q157" t="n">
+        <v>364282626</v>
+      </c>
     </row>
     <row r="158" ht="19" customHeight="1">
       <c r="A158" s="1" t="n">
@@ -9216,6 +9687,9 @@
       <c r="P158" t="n">
         <v>610</v>
       </c>
+      <c r="Q158" t="n">
+        <v>394464450</v>
+      </c>
     </row>
     <row r="159" ht="19" customHeight="1">
       <c r="A159" s="1" t="n">
@@ -9272,6 +9746,9 @@
       <c r="P159" t="n">
         <v>66</v>
       </c>
+      <c r="Q159" t="n">
+        <v>370786668</v>
+      </c>
     </row>
     <row r="160" ht="19" customHeight="1">
       <c r="A160" s="1" t="n">
@@ -9331,6 +9808,9 @@
       </c>
       <c r="P160" t="n">
         <v>91</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>372532958</v>
       </c>
     </row>
     <row r="161" ht="19" customHeight="1">
@@ -9380,6 +9860,9 @@
       <c r="P161" t="n">
         <v>202</v>
       </c>
+      <c r="Q161" t="n">
+        <v>396913794</v>
+      </c>
     </row>
     <row r="162" ht="19" customHeight="1">
       <c r="A162" s="1" t="n">
@@ -9434,6 +9917,9 @@
       <c r="P162" t="n">
         <v>76</v>
       </c>
+      <c r="Q162" t="n">
+        <v>372662796</v>
+      </c>
     </row>
     <row r="163" ht="19" customHeight="1">
       <c r="A163" s="1" t="n">
@@ -9486,6 +9972,9 @@
       <c r="P163" t="n">
         <v>184</v>
       </c>
+      <c r="Q163" t="n">
+        <v>374631364</v>
+      </c>
     </row>
     <row r="164" ht="19" customHeight="1">
       <c r="A164" s="1" t="n">
@@ -9542,6 +10031,9 @@
       <c r="P164" t="n">
         <v>108</v>
       </c>
+      <c r="Q164" t="n">
+        <v>402713176</v>
+      </c>
     </row>
     <row r="165" ht="19" customHeight="1">
       <c r="A165" s="1" t="n">
@@ -9602,6 +10094,9 @@
       <c r="P165" t="n">
         <v>163</v>
       </c>
+      <c r="Q165" t="n">
+        <v>365432766</v>
+      </c>
     </row>
     <row r="166" ht="19" customHeight="1">
       <c r="A166" s="1" t="n">
@@ -9661,6 +10156,9 @@
       </c>
       <c r="P166" t="n">
         <v>100</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>359921314</v>
       </c>
     </row>
     <row r="167" ht="19" customHeight="1">
@@ -9710,6 +10208,9 @@
       <c r="P167" t="n">
         <v>172</v>
       </c>
+      <c r="Q167" t="n">
+        <v>390718820</v>
+      </c>
     </row>
     <row r="168" ht="19" customHeight="1">
       <c r="A168" s="1" t="n">
@@ -9765,6 +10266,9 @@
       </c>
       <c r="P168" t="n">
         <v>252</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>358055754</v>
       </c>
     </row>
     <row r="169" ht="19" customHeight="1">
@@ -9806,6 +10310,9 @@
       <c r="P169" t="n">
         <v>128</v>
       </c>
+      <c r="Q169" t="n">
+        <v>364732942</v>
+      </c>
     </row>
     <row r="170" ht="19" customHeight="1">
       <c r="A170" s="1" t="n">
@@ -9859,6 +10366,9 @@
       </c>
       <c r="P170" t="n">
         <v>175</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>393592226</v>
       </c>
     </row>
     <row r="171" ht="19" customHeight="1">
@@ -9908,6 +10418,9 @@
       <c r="P171" t="n">
         <v>220</v>
       </c>
+      <c r="Q171" t="n">
+        <v>364444632</v>
+      </c>
     </row>
     <row r="172" ht="19" customHeight="1">
       <c r="A172" s="1" t="n">
@@ -9960,6 +10473,9 @@
       <c r="P172" t="n">
         <v>96</v>
       </c>
+      <c r="Q172" t="n">
+        <v>370869162</v>
+      </c>
     </row>
     <row r="173" ht="19" customHeight="1">
       <c r="A173" s="1" t="n">
@@ -10012,6 +10528,9 @@
       <c r="P173" t="n">
         <v>129</v>
       </c>
+      <c r="Q173" t="n">
+        <v>396617204</v>
+      </c>
     </row>
     <row r="174" ht="19" customHeight="1">
       <c r="A174" s="1" t="n">
@@ -10068,6 +10587,9 @@
       <c r="P174" t="n">
         <v>110</v>
       </c>
+      <c r="Q174" t="n">
+        <v>358436376</v>
+      </c>
     </row>
     <row r="175" ht="19" customHeight="1">
       <c r="A175" s="1" t="n">
@@ -10119,6 +10641,9 @@
       </c>
       <c r="P175" t="n">
         <v>127</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>335357710</v>
       </c>
     </row>
     <row r="176" ht="19" customHeight="1">
@@ -10172,6 +10697,9 @@
       <c r="P176" t="n">
         <v>197</v>
       </c>
+      <c r="Q176" t="n">
+        <v>390203400</v>
+      </c>
     </row>
     <row r="177" ht="19" customHeight="1">
       <c r="A177" s="1" t="n">
@@ -10232,6 +10760,9 @@
       <c r="P177" t="n">
         <v>64</v>
       </c>
+      <c r="Q177" t="n">
+        <v>360075550</v>
+      </c>
     </row>
     <row r="178" ht="19" customHeight="1">
       <c r="A178" s="1" t="n">
@@ -10287,6 +10818,9 @@
       </c>
       <c r="P178" t="n">
         <v>228</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>358471886</v>
       </c>
     </row>
     <row r="179" ht="19" customHeight="1">
@@ -10336,6 +10870,9 @@
       <c r="P179" t="n">
         <v>107</v>
       </c>
+      <c r="Q179" t="n">
+        <v>382962350</v>
+      </c>
     </row>
     <row r="180" ht="19" customHeight="1">
       <c r="A180" s="1" t="n">
@@ -10388,6 +10925,9 @@
       <c r="P180" t="n">
         <v>92</v>
       </c>
+      <c r="Q180" t="n">
+        <v>349981630</v>
+      </c>
     </row>
     <row r="181" ht="19" customHeight="1">
       <c r="A181" s="1" t="n">
@@ -10447,6 +10987,9 @@
       </c>
       <c r="P181" t="n">
         <v>232</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>351174612</v>
       </c>
     </row>
     <row r="182" ht="19" customHeight="1">
@@ -10500,6 +11043,9 @@
       <c r="P182" t="n">
         <v>134</v>
       </c>
+      <c r="Q182" t="n">
+        <v>376825490</v>
+      </c>
     </row>
     <row r="183" ht="19" customHeight="1">
       <c r="A183" s="1" t="n">
@@ -10560,6 +11106,9 @@
       <c r="P183" t="n">
         <v>219</v>
       </c>
+      <c r="Q183" t="n">
+        <v>352893610</v>
+      </c>
     </row>
     <row r="184" ht="19" customHeight="1">
       <c r="A184" s="1" t="n">
@@ -10620,6 +11169,9 @@
       <c r="P184" t="n">
         <v>66</v>
       </c>
+      <c r="Q184" t="n">
+        <v>363086950</v>
+      </c>
     </row>
     <row r="185" ht="19" customHeight="1">
       <c r="A185" s="1" t="n">
@@ -10682,6 +11234,9 @@
       <c r="P185" t="n">
         <v>53</v>
       </c>
+      <c r="Q185" t="n">
+        <v>387109286</v>
+      </c>
     </row>
     <row r="186" ht="19" customHeight="1">
       <c r="A186" s="1" t="n">
@@ -10738,6 +11293,9 @@
       <c r="P186" t="n">
         <v>144</v>
       </c>
+      <c r="Q186" t="n">
+        <v>355121956</v>
+      </c>
     </row>
     <row r="187" ht="19" customHeight="1">
       <c r="A187" s="1" t="n">
@@ -10798,6 +11356,9 @@
       <c r="P187" t="n">
         <v>141</v>
       </c>
+      <c r="Q187" t="n">
+        <v>360195880</v>
+      </c>
     </row>
     <row r="188" ht="19" customHeight="1">
       <c r="A188" s="1" t="n">
@@ -10858,6 +11419,9 @@
       <c r="P188" t="n">
         <v>99</v>
       </c>
+      <c r="Q188" t="n">
+        <v>386580634</v>
+      </c>
     </row>
     <row r="189" ht="19" customHeight="1">
       <c r="A189" s="1" t="n">
@@ -10914,6 +11478,9 @@
       <c r="P189" t="n">
         <v>97</v>
       </c>
+      <c r="Q189" t="n">
+        <v>356240472</v>
+      </c>
     </row>
     <row r="190" ht="19" customHeight="1">
       <c r="A190" s="1" t="n">
@@ -10969,6 +11536,9 @@
       </c>
       <c r="P190" t="n">
         <v>185</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>357436118</v>
       </c>
     </row>
     <row r="191" ht="19" customHeight="1">
@@ -11014,6 +11584,9 @@
       <c r="P191" t="n">
         <v>158</v>
       </c>
+      <c r="Q191" t="n">
+        <v>381153750</v>
+      </c>
     </row>
     <row r="192" ht="19" customHeight="1">
       <c r="A192" s="1" t="n">
@@ -11066,6 +11639,9 @@
       <c r="P192" t="n">
         <v>98</v>
       </c>
+      <c r="Q192" t="n">
+        <v>350096092</v>
+      </c>
     </row>
     <row r="193" ht="19" customHeight="1">
       <c r="A193" s="1" t="n">
@@ -11126,6 +11702,9 @@
       <c r="P193" t="n">
         <v>122</v>
       </c>
+      <c r="Q193" t="n">
+        <v>354904960</v>
+      </c>
     </row>
     <row r="194" ht="19" customHeight="1">
       <c r="A194" s="1" t="n">
@@ -11186,6 +11765,9 @@
       <c r="P194" t="n">
         <v>97</v>
       </c>
+      <c r="Q194" t="n">
+        <v>384947064</v>
+      </c>
     </row>
     <row r="195" ht="19" customHeight="1">
       <c r="A195" s="1" t="n">
@@ -11240,6 +11822,9 @@
       <c r="P195" t="n">
         <v>64</v>
       </c>
+      <c r="Q195" t="n">
+        <v>358375594</v>
+      </c>
     </row>
     <row r="196" ht="19" customHeight="1">
       <c r="A196" s="1" t="n">
@@ -11299,6 +11884,9 @@
       </c>
       <c r="P196" t="n">
         <v>98</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>357345052</v>
       </c>
     </row>
     <row r="197" ht="19" customHeight="1">
@@ -11354,6 +11942,9 @@
       <c r="P197" t="n">
         <v>55</v>
       </c>
+      <c r="Q197" t="n">
+        <v>382160878</v>
+      </c>
     </row>
     <row r="198" ht="19" customHeight="1">
       <c r="A198" s="1" t="n">
@@ -11414,6 +12005,9 @@
       <c r="P198" t="n">
         <v>62</v>
       </c>
+      <c r="Q198" t="n">
+        <v>353863692</v>
+      </c>
     </row>
     <row r="199" ht="19" customHeight="1">
       <c r="A199" s="1" t="n">
@@ -11470,6 +12064,9 @@
       <c r="P199" t="n">
         <v>342</v>
       </c>
+      <c r="Q199" t="n">
+        <v>357870744</v>
+      </c>
     </row>
     <row r="200" ht="19" customHeight="1">
       <c r="A200" s="1" t="n">
@@ -11532,6 +12129,9 @@
       <c r="P200" t="n">
         <v>125</v>
       </c>
+      <c r="Q200" t="n">
+        <v>387715200</v>
+      </c>
     </row>
     <row r="201" ht="19" customHeight="1">
       <c r="A201" s="1" t="n">
@@ -11588,6 +12188,9 @@
       <c r="P201" t="n">
         <v>225</v>
       </c>
+      <c r="Q201" t="n">
+        <v>357725994</v>
+      </c>
     </row>
     <row r="202" ht="19" customHeight="1">
       <c r="A202" s="1" t="n">
@@ -11648,6 +12251,9 @@
       <c r="P202" t="n">
         <v>266</v>
       </c>
+      <c r="Q202" t="n">
+        <v>362199042</v>
+      </c>
     </row>
     <row r="203" ht="19" customHeight="1">
       <c r="A203" s="1" t="n">
@@ -11702,6 +12308,9 @@
       <c r="P203" t="n">
         <v>82</v>
       </c>
+      <c r="Q203" t="n">
+        <v>390452378</v>
+      </c>
     </row>
     <row r="204" ht="19" customHeight="1">
       <c r="A204" s="1" t="n">
@@ -11758,6 +12367,9 @@
       <c r="P204" t="n">
         <v>243</v>
       </c>
+      <c r="Q204" t="n">
+        <v>359711540</v>
+      </c>
     </row>
     <row r="205" ht="19" customHeight="1">
       <c r="A205" s="1" t="n">
@@ -11812,6 +12424,9 @@
       <c r="P205" t="n">
         <v>164</v>
       </c>
+      <c r="Q205" t="n">
+        <v>370629284</v>
+      </c>
     </row>
     <row r="206" ht="19" customHeight="1">
       <c r="A206" s="1" t="n">
@@ -11874,6 +12489,9 @@
       <c r="P206" t="n">
         <v>98</v>
       </c>
+      <c r="Q206" t="n">
+        <v>408618502</v>
+      </c>
     </row>
     <row r="207" ht="19" customHeight="1">
       <c r="A207" s="1" t="n">
@@ -11934,6 +12552,9 @@
       <c r="P207" t="n">
         <v>103</v>
       </c>
+      <c r="Q207" t="n">
+        <v>370559376</v>
+      </c>
     </row>
     <row r="208" ht="19" customHeight="1">
       <c r="A208" s="1" t="n">
@@ -11993,6 +12614,9 @@
       </c>
       <c r="P208" t="n">
         <v>76</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>371735912</v>
       </c>
     </row>
     <row r="209" ht="19" customHeight="1">
@@ -12038,6 +12662,9 @@
       <c r="P209" t="n">
         <v>77</v>
       </c>
+      <c r="Q209" t="n">
+        <v>405852212</v>
+      </c>
     </row>
     <row r="210" ht="19" customHeight="1">
       <c r="A210" s="1" t="n">
@@ -12094,6 +12721,9 @@
       <c r="P210" t="n">
         <v>140</v>
       </c>
+      <c r="Q210" t="n">
+        <v>375981944</v>
+      </c>
     </row>
     <row r="211" ht="19" customHeight="1">
       <c r="A211" s="1" t="n">
@@ -12146,6 +12776,9 @@
       <c r="P211" t="n">
         <v>194</v>
       </c>
+      <c r="Q211" t="n">
+        <v>377747376</v>
+      </c>
     </row>
     <row r="212" ht="19" customHeight="1">
       <c r="A212" s="1" t="n">
@@ -12200,6 +12833,9 @@
       <c r="P212" t="n">
         <v>109</v>
       </c>
+      <c r="Q212" t="n">
+        <v>414140392</v>
+      </c>
     </row>
     <row r="213" ht="19" customHeight="1">
       <c r="A213" s="1" t="n">
@@ -12253,6 +12889,9 @@
       </c>
       <c r="P213" t="n">
         <v>221</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>372318810</v>
       </c>
     </row>
     <row r="214" ht="19" customHeight="1">
@@ -12298,6 +12937,9 @@
       <c r="P214" t="n">
         <v>70</v>
       </c>
+      <c r="Q214" t="n">
+        <v>375580258</v>
+      </c>
     </row>
     <row r="215" ht="19" customHeight="1">
       <c r="A215" s="1" t="n">
@@ -12352,6 +12994,9 @@
       <c r="P215" t="n">
         <v>121</v>
       </c>
+      <c r="Q215" t="n">
+        <v>404303630</v>
+      </c>
     </row>
     <row r="216" ht="19" customHeight="1">
       <c r="A216" s="1" t="n">
@@ -12411,6 +13056,9 @@
       </c>
       <c r="P216" t="n">
         <v>176</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>369828352</v>
       </c>
     </row>
     <row r="217" ht="19" customHeight="1">
@@ -12464,6 +13112,9 @@
       <c r="P217" t="n">
         <v>101</v>
       </c>
+      <c r="Q217" t="n">
+        <v>373161172</v>
+      </c>
     </row>
     <row r="218" ht="19" customHeight="1">
       <c r="A218" s="1" t="n">
@@ -12520,6 +13171,9 @@
       <c r="P218" t="n">
         <v>157</v>
       </c>
+      <c r="Q218" t="n">
+        <v>370562742</v>
+      </c>
     </row>
     <row r="219" ht="19" customHeight="1">
       <c r="A219" s="1" t="n">
@@ -12581,6 +13235,9 @@
       </c>
       <c r="P219" t="n">
         <v>123</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>399381218</v>
       </c>
     </row>
     <row r="220" ht="19" customHeight="1">
@@ -12636,6 +13293,9 @@
       <c r="P220" t="n">
         <v>238</v>
       </c>
+      <c r="Q220" t="n">
+        <v>373229184</v>
+      </c>
     </row>
     <row r="221" ht="19" customHeight="1">
       <c r="A221" s="1" t="n">
@@ -12696,6 +13356,9 @@
       <c r="P221" t="n">
         <v>114</v>
       </c>
+      <c r="Q221" t="n">
+        <v>382441836</v>
+      </c>
     </row>
     <row r="222" ht="19" customHeight="1">
       <c r="A222" s="1" t="n">
@@ -12758,6 +13421,9 @@
       <c r="P222" t="n">
         <v>400</v>
       </c>
+      <c r="Q222" t="n">
+        <v>416077564</v>
+      </c>
     </row>
     <row r="223" ht="19" customHeight="1">
       <c r="A223" s="1" t="n">
@@ -12820,6 +13486,9 @@
       <c r="P223" t="n">
         <v>76</v>
       </c>
+      <c r="Q223" t="n">
+        <v>379869478</v>
+      </c>
     </row>
     <row r="224" ht="19" customHeight="1">
       <c r="A224" s="1" t="n">
@@ -12872,6 +13541,9 @@
       <c r="P224" t="n">
         <v>262</v>
       </c>
+      <c r="Q224" t="n">
+        <v>382480862</v>
+      </c>
     </row>
     <row r="225" ht="19" customHeight="1">
       <c r="A225" s="1" t="n">
@@ -12928,6 +13600,9 @@
       <c r="P225" t="n">
         <v>105</v>
       </c>
+      <c r="Q225" t="n">
+        <v>412907242</v>
+      </c>
     </row>
     <row r="226" ht="19" customHeight="1">
       <c r="A226" s="1" t="n">
@@ -12987,6 +13662,9 @@
       </c>
       <c r="P226" t="n">
         <v>104</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>383794308</v>
       </c>
     </row>
     <row r="227" ht="19" customHeight="1">
@@ -13036,6 +13714,9 @@
       <c r="P227" t="n">
         <v>146</v>
       </c>
+      <c r="Q227" t="n">
+        <v>385283048</v>
+      </c>
     </row>
     <row r="228" ht="19" customHeight="1">
       <c r="A228" s="1" t="n">
@@ -13084,6 +13765,9 @@
       <c r="P228" t="n">
         <v>207</v>
       </c>
+      <c r="Q228" t="n">
+        <v>417825112</v>
+      </c>
     </row>
     <row r="229" ht="19" customHeight="1">
       <c r="A229" s="1" t="n">
@@ -13136,6 +13820,9 @@
       <c r="P229" t="n">
         <v>104</v>
       </c>
+      <c r="Q229" t="n">
+        <v>386307316</v>
+      </c>
     </row>
     <row r="230" ht="19" customHeight="1">
       <c r="A230" s="1" t="n">
@@ -13184,6 +13871,9 @@
       <c r="P230" t="n">
         <v>140</v>
       </c>
+      <c r="Q230" t="n">
+        <v>394649530</v>
+      </c>
     </row>
     <row r="231" ht="19" customHeight="1">
       <c r="A231" s="1" t="n">
@@ -13236,6 +13926,9 @@
       <c r="P231" t="n">
         <v>253</v>
       </c>
+      <c r="Q231" t="n">
+        <v>415967168</v>
+      </c>
     </row>
     <row r="232" ht="19" customHeight="1">
       <c r="A232" s="1" t="n">
@@ -13292,6 +13985,9 @@
       <c r="P232" t="n">
         <v>178</v>
       </c>
+      <c r="Q232" t="n">
+        <v>381237932</v>
+      </c>
     </row>
     <row r="233" ht="19" customHeight="1">
       <c r="A233" s="1" t="n">
@@ -13352,6 +14048,9 @@
       <c r="P233" t="n">
         <v>132</v>
       </c>
+      <c r="Q233" t="n">
+        <v>473959588</v>
+      </c>
     </row>
     <row r="234" ht="19" customHeight="1">
       <c r="A234" s="1" t="n">
@@ -13414,6 +14113,9 @@
       <c r="P234" t="n">
         <v>261</v>
       </c>
+      <c r="Q234" t="n">
+        <v>497696868</v>
+      </c>
     </row>
     <row r="235" ht="19" customHeight="1">
       <c r="A235" s="1" t="n">
@@ -13473,6 +14175,9 @@
       </c>
       <c r="P235" t="n">
         <v>140</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>466031504</v>
       </c>
     </row>
     <row r="236" ht="19" customHeight="1">
@@ -13522,6 +14227,9 @@
       <c r="P236" t="n">
         <v>339</v>
       </c>
+      <c r="Q236" t="n">
+        <v>474511672</v>
+      </c>
     </row>
     <row r="237" ht="19" customHeight="1">
       <c r="A237" s="1" t="n">
@@ -13581,6 +14289,9 @@
       </c>
       <c r="P237" t="n">
         <v>306</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>517770956</v>
       </c>
     </row>
     <row r="238" ht="19" customHeight="1">
@@ -13636,6 +14347,9 @@
       <c r="P238" t="n">
         <v>232</v>
       </c>
+      <c r="Q238" t="n">
+        <v>484355844</v>
+      </c>
     </row>
     <row r="239" ht="19" customHeight="1">
       <c r="A239" s="1" t="n">
@@ -13688,6 +14402,9 @@
       <c r="P239" t="n">
         <v>221</v>
       </c>
+      <c r="Q239" t="n">
+        <v>486609550</v>
+      </c>
     </row>
     <row r="240" ht="19" customHeight="1">
       <c r="A240" s="1" t="n">
@@ -13740,6 +14457,9 @@
       <c r="P240" t="n">
         <v>240</v>
       </c>
+      <c r="Q240" t="n">
+        <v>525192790</v>
+      </c>
     </row>
     <row r="241" ht="19" customHeight="1">
       <c r="A241" s="1" t="n">
@@ -13792,6 +14512,9 @@
       <c r="P241" t="n">
         <v>213</v>
       </c>
+      <c r="Q241" t="n">
+        <v>492348152</v>
+      </c>
     </row>
     <row r="242" ht="19" customHeight="1">
       <c r="A242" s="1" t="n">
@@ -13852,6 +14575,9 @@
       <c r="P242" t="n">
         <v>78</v>
       </c>
+      <c r="Q242" t="n">
+        <v>492601986</v>
+      </c>
     </row>
     <row r="243" ht="19" customHeight="1">
       <c r="A243" s="1" t="n">
@@ -13904,6 +14630,9 @@
       <c r="P243" t="n">
         <v>133</v>
       </c>
+      <c r="Q243" t="n">
+        <v>521719600</v>
+      </c>
     </row>
     <row r="244" ht="19" customHeight="1">
       <c r="A244" s="1" t="n">
@@ -13966,6 +14695,9 @@
       <c r="P244" t="n">
         <v>123</v>
       </c>
+      <c r="Q244" t="n">
+        <v>480392100</v>
+      </c>
     </row>
     <row r="245" ht="19" customHeight="1">
       <c r="A245" s="1" t="n">
@@ -14025,6 +14757,9 @@
       </c>
       <c r="P245" t="n">
         <v>220</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>493963074</v>
       </c>
     </row>
     <row r="246" ht="19" customHeight="1">
@@ -14079,6 +14814,9 @@
       </c>
       <c r="P246" t="n">
         <v>130</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>507406422</v>
       </c>
     </row>
     <row r="247" ht="19" customHeight="1">
@@ -14120,6 +14858,9 @@
       <c r="P247" t="n">
         <v>187</v>
       </c>
+      <c r="Q247" t="n">
+        <v>460243432</v>
+      </c>
     </row>
     <row r="248" ht="19" customHeight="1">
       <c r="A248" s="1" t="n">
@@ -14179,6 +14920,9 @@
       </c>
       <c r="P248" t="n">
         <v>151</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>461560620</v>
       </c>
     </row>
     <row r="249" ht="19" customHeight="1">
@@ -14232,6 +14976,9 @@
       <c r="P249" t="n">
         <v>195</v>
       </c>
+      <c r="Q249" t="n">
+        <v>488324570</v>
+      </c>
     </row>
     <row r="250" ht="19" customHeight="1">
       <c r="A250" s="1" t="n">
@@ -14288,6 +15035,9 @@
       <c r="P250" t="n">
         <v>172</v>
       </c>
+      <c r="Q250" t="n">
+        <v>449833942</v>
+      </c>
     </row>
     <row r="251" ht="19" customHeight="1">
       <c r="A251" s="1" t="n">
@@ -14350,6 +15100,9 @@
       <c r="P251" t="n">
         <v>96</v>
       </c>
+      <c r="Q251" t="n">
+        <v>432874498</v>
+      </c>
     </row>
     <row r="252" ht="19" customHeight="1">
       <c r="A252" s="1" t="n">
@@ -14411,6 +15164,9 @@
       </c>
       <c r="P252" t="n">
         <v>424</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>454223900</v>
       </c>
     </row>
     <row r="253" ht="19" customHeight="1">
@@ -14456,6 +15212,9 @@
       <c r="P253" t="n">
         <v>134</v>
       </c>
+      <c r="Q253" t="n">
+        <v>405361488</v>
+      </c>
     </row>
     <row r="254" ht="19" customHeight="1">
       <c r="A254" s="1" t="n">
@@ -14518,6 +15277,9 @@
       <c r="P254" t="n">
         <v>109</v>
       </c>
+      <c r="Q254" t="n">
+        <v>411922624</v>
+      </c>
     </row>
     <row r="255" ht="19" customHeight="1">
       <c r="A255" s="1" t="n">
@@ -14578,6 +15340,9 @@
       <c r="P255" t="n">
         <v>112</v>
       </c>
+      <c r="Q255" t="n">
+        <v>452958034</v>
+      </c>
     </row>
     <row r="256" ht="19" customHeight="1">
       <c r="A256" s="1" t="n">
@@ -14640,6 +15405,9 @@
       <c r="P256" t="n">
         <v>164</v>
       </c>
+      <c r="Q256" t="n">
+        <v>397951464</v>
+      </c>
     </row>
     <row r="257" ht="19" customHeight="1">
       <c r="A257" s="1" t="n">
@@ -14696,6 +15464,9 @@
       <c r="P257" t="n">
         <v>196</v>
       </c>
+      <c r="Q257" t="n">
+        <v>402054502</v>
+      </c>
     </row>
     <row r="258" ht="19" customHeight="1">
       <c r="A258" s="1" t="n">
@@ -14752,6 +15523,9 @@
       <c r="P258" t="n">
         <v>116</v>
       </c>
+      <c r="Q258" t="n">
+        <v>428830208</v>
+      </c>
     </row>
     <row r="259" ht="19" customHeight="1">
       <c r="A259" s="1" t="n">
@@ -14812,6 +15586,9 @@
       <c r="P259" t="n">
         <v>163</v>
       </c>
+      <c r="Q259" t="n">
+        <v>397770990</v>
+      </c>
     </row>
     <row r="260" ht="19" customHeight="1">
       <c r="A260" s="1" t="n">
@@ -14867,6 +15644,9 @@
       </c>
       <c r="P260" t="n">
         <v>99</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>407820678</v>
       </c>
     </row>
     <row r="261" ht="19" customHeight="1">
@@ -14922,6 +15702,9 @@
       <c r="P261" t="n">
         <v>98</v>
       </c>
+      <c r="Q261" t="n">
+        <v>430067550</v>
+      </c>
     </row>
     <row r="262" ht="19" customHeight="1">
       <c r="A262" s="1" t="n">
@@ -14976,6 +15759,9 @@
       <c r="P262" t="n">
         <v>178</v>
       </c>
+      <c r="Q262" t="n">
+        <v>391831746</v>
+      </c>
     </row>
     <row r="263" ht="19" customHeight="1">
       <c r="A263" s="1" t="n">
@@ -15036,6 +15822,9 @@
       <c r="P263" t="n">
         <v>151</v>
       </c>
+      <c r="Q263" t="n">
+        <v>390103204</v>
+      </c>
     </row>
     <row r="264" ht="19" customHeight="1">
       <c r="A264" s="1" t="n">
@@ -15088,6 +15877,9 @@
       <c r="P264" t="n">
         <v>118</v>
       </c>
+      <c r="Q264" t="n">
+        <v>409759128</v>
+      </c>
     </row>
     <row r="265" ht="19" customHeight="1">
       <c r="A265" s="1" t="n">
@@ -15147,6 +15939,9 @@
       </c>
       <c r="P265" t="n">
         <v>73</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>372460178</v>
       </c>
     </row>
     <row r="266" ht="19" customHeight="1">
@@ -15194,6 +15989,9 @@
       <c r="P266" t="n">
         <v>143</v>
       </c>
+      <c r="Q266" t="n">
+        <v>382080084</v>
+      </c>
     </row>
     <row r="267" ht="19" customHeight="1">
       <c r="A267" s="1" t="n">
@@ -15242,6 +16040,9 @@
       <c r="P267" t="n">
         <v>138</v>
       </c>
+      <c r="Q267" t="n">
+        <v>406461312</v>
+      </c>
     </row>
     <row r="268" ht="19" customHeight="1">
       <c r="A268" s="1" t="n">
@@ -15296,6 +16097,9 @@
       <c r="P268" t="n">
         <v>149</v>
       </c>
+      <c r="Q268" t="n">
+        <v>368057096</v>
+      </c>
     </row>
     <row r="269" ht="19" customHeight="1">
       <c r="A269" s="1" t="n">
@@ -15358,6 +16162,9 @@
       <c r="P269" t="n">
         <v>110</v>
       </c>
+      <c r="Q269" t="n">
+        <v>369008560</v>
+      </c>
     </row>
     <row r="270" ht="19" customHeight="1">
       <c r="A270" s="1" t="n">
@@ -15414,6 +16221,9 @@
       <c r="P270" t="n">
         <v>254</v>
       </c>
+      <c r="Q270" t="n">
+        <v>391425990</v>
+      </c>
     </row>
     <row r="271" ht="19" customHeight="1">
       <c r="A271" s="1" t="n">
@@ -15473,6 +16283,9 @@
       </c>
       <c r="P271" t="n">
         <v>87</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>398150146</v>
       </c>
     </row>
     <row r="272" ht="19" customHeight="1">
@@ -15528,6 +16341,9 @@
       <c r="P272" t="n">
         <v>96</v>
       </c>
+      <c r="Q272" t="n">
+        <v>408414594</v>
+      </c>
     </row>
     <row r="273" ht="19" customHeight="1">
       <c r="A273" s="1" t="n">
@@ -15580,6 +16396,9 @@
       <c r="P273" t="n">
         <v>224</v>
       </c>
+      <c r="Q273" t="n">
+        <v>362234554</v>
+      </c>
     </row>
     <row r="274" ht="19" customHeight="1">
       <c r="A274" s="1" t="n">
@@ -15632,6 +16451,9 @@
       <c r="P274" t="n">
         <v>107</v>
       </c>
+      <c r="Q274" t="n">
+        <v>362006810</v>
+      </c>
     </row>
     <row r="275" ht="19" customHeight="1">
       <c r="A275" s="1" t="n">
@@ -15686,6 +16508,9 @@
       <c r="P275" t="n">
         <v>65</v>
       </c>
+      <c r="Q275" t="n">
+        <v>401743532</v>
+      </c>
     </row>
     <row r="276" ht="19" customHeight="1">
       <c r="A276" s="1" t="n">
@@ -15745,6 +16570,9 @@
       </c>
       <c r="P276" t="n">
         <v>182</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>387567590</v>
       </c>
     </row>
     <row r="277" ht="19" customHeight="1">
@@ -15786,6 +16614,9 @@
       <c r="P277" t="n">
         <v>335</v>
       </c>
+      <c r="Q277" t="n">
+        <v>388759926</v>
+      </c>
     </row>
     <row r="278" ht="19" customHeight="1">
       <c r="A278" s="1" t="n">
@@ -15833,6 +16664,9 @@
       </c>
       <c r="P278" t="n">
         <v>174</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>429941270</v>
       </c>
     </row>
     <row r="279" ht="19" customHeight="1">
@@ -15874,6 +16708,9 @@
       <c r="P279" t="n">
         <v>276</v>
       </c>
+      <c r="Q279" t="n">
+        <v>389179240</v>
+      </c>
     </row>
     <row r="280" ht="19" customHeight="1">
       <c r="A280" s="1" t="n">
@@ -15933,6 +16770,9 @@
       </c>
       <c r="P280" t="n">
         <v>77</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>399059370</v>
       </c>
     </row>
     <row r="281" ht="19" customHeight="1">
@@ -15986,6 +16826,9 @@
       <c r="P281" t="n">
         <v>465</v>
       </c>
+      <c r="Q281" t="n">
+        <v>431419382</v>
+      </c>
     </row>
     <row r="282" ht="19" customHeight="1">
       <c r="A282" s="1" t="n">
@@ -16042,6 +16885,9 @@
       <c r="P282" t="n">
         <v>296</v>
       </c>
+      <c r="Q282" t="n">
+        <v>398514350</v>
+      </c>
     </row>
     <row r="283" ht="19" customHeight="1">
       <c r="A283" s="1" t="n">
@@ -16098,6 +16944,9 @@
       <c r="P283" t="n">
         <v>206</v>
       </c>
+      <c r="Q283" t="n">
+        <v>400874276</v>
+      </c>
     </row>
     <row r="284" ht="19" customHeight="1">
       <c r="A284" s="1" t="n">
@@ -16149,6 +16998,9 @@
       </c>
       <c r="P284" t="n">
         <v>116</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>433441094</v>
       </c>
     </row>
     <row r="285" ht="19" customHeight="1">
@@ -16196,6 +17048,9 @@
       <c r="P285" t="n">
         <v>76</v>
       </c>
+      <c r="Q285" t="n">
+        <v>398025748</v>
+      </c>
     </row>
     <row r="286" ht="19" customHeight="1">
       <c r="A286" s="1" t="n">
@@ -16256,6 +17111,9 @@
       <c r="P286" t="n">
         <v>173</v>
       </c>
+      <c r="Q286" t="n">
+        <v>401159328</v>
+      </c>
     </row>
     <row r="287" ht="19" customHeight="1">
       <c r="A287" s="1" t="n">
@@ -16312,6 +17170,9 @@
       <c r="P287" t="n">
         <v>135</v>
       </c>
+      <c r="Q287" t="n">
+        <v>413703736</v>
+      </c>
     </row>
     <row r="288" ht="19" customHeight="1">
       <c r="A288" s="1" t="n">
@@ -16371,6 +17232,9 @@
       </c>
       <c r="P288" t="n">
         <v>117</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>374362318</v>
       </c>
     </row>
     <row r="289" ht="19" customHeight="1">
@@ -16420,6 +17284,9 @@
       <c r="P289" t="n">
         <v>248</v>
       </c>
+      <c r="Q289" t="n">
+        <v>385412112</v>
+      </c>
     </row>
     <row r="290" ht="19" customHeight="1">
       <c r="A290" s="1" t="n">
@@ -16468,6 +17335,9 @@
       <c r="P290" t="n">
         <v>504</v>
       </c>
+      <c r="Q290" t="n">
+        <v>412436132</v>
+      </c>
     </row>
     <row r="291" ht="19" customHeight="1">
       <c r="A291" s="1" t="n">
@@ -16524,6 +17394,9 @@
       <c r="P291" t="n">
         <v>206</v>
       </c>
+      <c r="Q291" t="n">
+        <v>375133272</v>
+      </c>
     </row>
     <row r="292" ht="19" customHeight="1">
       <c r="A292" s="1" t="n">
@@ -16583,6 +17456,9 @@
       </c>
       <c r="P292" t="n">
         <v>90</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>356283280</v>
       </c>
     </row>
     <row r="293" ht="19" customHeight="1">
@@ -16632,6 +17508,9 @@
       <c r="P293" t="n">
         <v>190</v>
       </c>
+      <c r="Q293" t="n">
+        <v>403976694</v>
+      </c>
     </row>
     <row r="294" ht="19" customHeight="1">
       <c r="A294" s="1" t="n">
@@ -16691,6 +17570,9 @@
       </c>
       <c r="P294" t="n">
         <v>138</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>381702830</v>
       </c>
     </row>
     <row r="295" ht="19" customHeight="1">
@@ -16739,6 +17621,9 @@
       </c>
       <c r="P295" t="n">
         <v>213</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>386011398</v>
       </c>
     </row>
     <row r="296" ht="19" customHeight="1">
@@ -16788,6 +17673,9 @@
       <c r="P296" t="n">
         <v>542</v>
       </c>
+      <c r="Q296" t="n">
+        <v>412186810</v>
+      </c>
     </row>
     <row r="297" ht="19" customHeight="1">
       <c r="A297" s="1" t="n">
@@ -16848,6 +17736,9 @@
       <c r="P297" t="n">
         <v>46</v>
       </c>
+      <c r="Q297" t="n">
+        <v>385020364</v>
+      </c>
     </row>
     <row r="298" ht="19" customHeight="1">
       <c r="A298" s="1" t="n">
@@ -16910,6 +17801,9 @@
       <c r="P298" t="n">
         <v>146</v>
       </c>
+      <c r="Q298" t="n">
+        <v>379945476</v>
+      </c>
     </row>
     <row r="299" ht="19" customHeight="1">
       <c r="A299" s="1" t="n">
@@ -16969,6 +17863,9 @@
       </c>
       <c r="P299" t="n">
         <v>115</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>405727312</v>
       </c>
     </row>
     <row r="300" ht="19" customHeight="1">
@@ -17022,6 +17919,9 @@
       <c r="P300" t="n">
         <v>334</v>
       </c>
+      <c r="Q300" t="n">
+        <v>379451774</v>
+      </c>
     </row>
     <row r="301" ht="19" customHeight="1">
       <c r="A301" s="1" t="n">
@@ -17074,6 +17974,9 @@
       <c r="P301" t="n">
         <v>188</v>
       </c>
+      <c r="Q301" t="n">
+        <v>382103034</v>
+      </c>
     </row>
     <row r="302" ht="19" customHeight="1">
       <c r="A302" s="1" t="n">
@@ -17126,6 +18029,9 @@
       <c r="P302" t="n">
         <v>91</v>
       </c>
+      <c r="Q302" t="n">
+        <v>405356264</v>
+      </c>
     </row>
     <row r="303" ht="19" customHeight="1">
       <c r="A303" s="1" t="n">
@@ -17178,6 +18084,9 @@
       <c r="P303" t="n">
         <v>114</v>
       </c>
+      <c r="Q303" t="n">
+        <v>351928312</v>
+      </c>
     </row>
     <row r="304" ht="19" customHeight="1">
       <c r="A304" s="1" t="n">
@@ -17231,6 +18140,9 @@
       </c>
       <c r="P304" t="n">
         <v>141</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>330045974</v>
       </c>
     </row>
     <row r="305" ht="19" customHeight="1">
@@ -17280,6 +18192,9 @@
       <c r="P305" t="n">
         <v>226</v>
       </c>
+      <c r="Q305" t="n">
+        <v>388201440</v>
+      </c>
     </row>
     <row r="306" ht="19" customHeight="1">
       <c r="A306" s="1" t="n">
@@ -17328,6 +18243,9 @@
       <c r="P306" t="n">
         <v>203</v>
       </c>
+      <c r="Q306" t="n">
+        <v>367939562</v>
+      </c>
     </row>
     <row r="307" ht="19" customHeight="1">
       <c r="A307" s="1" t="n">
@@ -17383,6 +18301,9 @@
       </c>
       <c r="P307" t="n">
         <v>131</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>373167274</v>
       </c>
     </row>
     <row r="308" ht="19" customHeight="1">
@@ -17438,6 +18359,9 @@
       <c r="P308" t="n">
         <v>220</v>
       </c>
+      <c r="Q308" t="n">
+        <v>395915432</v>
+      </c>
     </row>
     <row r="309" ht="19" customHeight="1">
       <c r="A309" s="1" t="n">
@@ -17486,6 +18410,9 @@
       <c r="P309" t="n">
         <v>242</v>
       </c>
+      <c r="Q309" t="n">
+        <v>367543408</v>
+      </c>
     </row>
     <row r="310" ht="19" customHeight="1">
       <c r="A310" s="1" t="n">
@@ -17542,6 +18469,9 @@
       <c r="P310" t="n">
         <v>144</v>
       </c>
+      <c r="Q310" t="n">
+        <v>377710122</v>
+      </c>
     </row>
     <row r="311" ht="19" customHeight="1">
       <c r="A311" s="1" t="n">
@@ -17598,6 +18528,9 @@
       <c r="P311" t="n">
         <v>97</v>
       </c>
+      <c r="Q311" t="n">
+        <v>397159810</v>
+      </c>
     </row>
     <row r="312" ht="19" customHeight="1">
       <c r="A312" s="1" t="n">
@@ -17658,6 +18591,9 @@
       <c r="P312" t="n">
         <v>384</v>
       </c>
+      <c r="Q312" t="n">
+        <v>365625592</v>
+      </c>
     </row>
     <row r="313" ht="19" customHeight="1">
       <c r="A313" s="1" t="n">
@@ -17719,6 +18655,9 @@
       </c>
       <c r="P313" t="n">
         <v>84</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>369285740</v>
       </c>
     </row>
     <row r="314" ht="19" customHeight="1">
@@ -17768,6 +18707,9 @@
       <c r="P314" t="n">
         <v>137</v>
       </c>
+      <c r="Q314" t="n">
+        <v>390426128</v>
+      </c>
     </row>
     <row r="315" ht="19" customHeight="1">
       <c r="A315" s="1" t="n">
@@ -17828,6 +18770,9 @@
       <c r="P315" t="n">
         <v>122</v>
       </c>
+      <c r="Q315" t="n">
+        <v>358843202</v>
+      </c>
     </row>
     <row r="316" ht="19" customHeight="1">
       <c r="A316" s="1" t="n">
@@ -17882,6 +18827,9 @@
       <c r="P316" t="n">
         <v>143</v>
       </c>
+      <c r="Q316" t="n">
+        <v>364421040</v>
+      </c>
     </row>
     <row r="317" ht="19" customHeight="1">
       <c r="A317" s="1" t="n">
@@ -17935,6 +18883,9 @@
       </c>
       <c r="P317" t="n">
         <v>90</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>390275626</v>
       </c>
     </row>
     <row r="318" ht="19" customHeight="1">
@@ -17982,6 +18933,9 @@
       <c r="P318" t="n">
         <v>245</v>
       </c>
+      <c r="Q318" t="n">
+        <v>362508790</v>
+      </c>
     </row>
     <row r="319" ht="19" customHeight="1">
       <c r="A319" s="1" t="n">
@@ -18042,6 +18996,9 @@
       <c r="P319" t="n">
         <v>277</v>
       </c>
+      <c r="Q319" t="n">
+        <v>365056746</v>
+      </c>
     </row>
     <row r="320" ht="19" customHeight="1">
       <c r="A320" s="1" t="n">
@@ -18098,6 +19055,9 @@
       <c r="P320" t="n">
         <v>236</v>
       </c>
+      <c r="Q320" t="n">
+        <v>373231796</v>
+      </c>
     </row>
     <row r="321" ht="19" customHeight="1">
       <c r="A321" s="1" t="n">
@@ -18159,6 +19119,9 @@
       </c>
       <c r="P321" t="n">
         <v>168</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>348630430</v>
       </c>
     </row>
     <row r="322" ht="19" customHeight="1">
@@ -18208,6 +19171,9 @@
       <c r="P322" t="n">
         <v>100</v>
       </c>
+      <c r="Q322" t="n">
+        <v>359572106</v>
+      </c>
     </row>
     <row r="323" ht="19" customHeight="1">
       <c r="A323" s="1" t="n">
@@ -18267,6 +19233,9 @@
       </c>
       <c r="P323" t="n">
         <v>190</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>382798116</v>
       </c>
     </row>
     <row r="324" ht="19" customHeight="1">
@@ -18322,6 +19291,9 @@
       <c r="P324" t="n">
         <v>121</v>
       </c>
+      <c r="Q324" t="n">
+        <v>349312006</v>
+      </c>
     </row>
     <row r="325" ht="19" customHeight="1">
       <c r="A325" s="1" t="n">
@@ -18376,6 +19348,9 @@
       <c r="P325" t="n">
         <v>95</v>
       </c>
+      <c r="Q325" t="n">
+        <v>355743106</v>
+      </c>
     </row>
     <row r="326" ht="19" customHeight="1">
       <c r="A326" s="1" t="n">
@@ -18436,6 +19411,9 @@
       <c r="P326" t="n">
         <v>130</v>
       </c>
+      <c r="Q326" t="n">
+        <v>377739850</v>
+      </c>
     </row>
     <row r="327" ht="19" customHeight="1">
       <c r="A327" s="1" t="n">
@@ -18491,6 +19469,9 @@
       </c>
       <c r="P327" t="n">
         <v>96</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>342963952</v>
       </c>
     </row>
     <row r="328" ht="19" customHeight="1">
@@ -18540,6 +19521,9 @@
       <c r="P328" t="n">
         <v>288</v>
       </c>
+      <c r="Q328" t="n">
+        <v>351823400</v>
+      </c>
     </row>
     <row r="329" ht="19" customHeight="1">
       <c r="A329" s="1" t="n">
@@ -18596,6 +19580,9 @@
       <c r="P329" t="n">
         <v>90</v>
       </c>
+      <c r="Q329" t="n">
+        <v>375016018</v>
+      </c>
     </row>
     <row r="330" ht="19" customHeight="1">
       <c r="A330" s="1" t="n">
@@ -18650,6 +19637,9 @@
       <c r="P330" t="n">
         <v>320</v>
       </c>
+      <c r="Q330" t="n">
+        <v>345694980</v>
+      </c>
     </row>
     <row r="331" ht="19" customHeight="1">
       <c r="A331" s="1" t="n">
@@ -18704,6 +19694,9 @@
       <c r="P331" t="n">
         <v>80</v>
       </c>
+      <c r="Q331" t="n">
+        <v>348856354</v>
+      </c>
     </row>
     <row r="332" ht="19" customHeight="1">
       <c r="A332" s="1" t="n">
@@ -18755,6 +19748,9 @@
       </c>
       <c r="P332" t="n">
         <v>92</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>369020954</v>
       </c>
     </row>
     <row r="333" ht="19" customHeight="1">
@@ -18810,6 +19806,9 @@
       <c r="P333" t="n">
         <v>171</v>
       </c>
+      <c r="Q333" t="n">
+        <v>342123330</v>
+      </c>
     </row>
     <row r="334" ht="19" customHeight="1">
       <c r="A334" s="1" t="n">
@@ -18869,6 +19868,9 @@
       </c>
       <c r="P334" t="n">
         <v>324</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>351442404</v>
       </c>
     </row>
     <row r="335" ht="19" customHeight="1">
@@ -18921,6 +19923,9 @@
       </c>
       <c r="P335" t="n">
         <v>197</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>375983952</v>
       </c>
     </row>
     <row r="336" ht="19" customHeight="1">
@@ -18968,6 +19973,9 @@
       <c r="P336" t="n">
         <v>501</v>
       </c>
+      <c r="Q336" t="n">
+        <v>351219750</v>
+      </c>
     </row>
     <row r="337" ht="19" customHeight="1">
       <c r="A337" s="1" t="n">
@@ -19022,6 +20030,9 @@
       <c r="P337" t="n">
         <v>89</v>
       </c>
+      <c r="Q337" t="n">
+        <v>350123408</v>
+      </c>
     </row>
     <row r="338" ht="19" customHeight="1">
       <c r="A338" s="1" t="n">
@@ -19082,6 +20093,9 @@
       <c r="P338" t="n">
         <v>101</v>
       </c>
+      <c r="Q338" t="n">
+        <v>378567992</v>
+      </c>
     </row>
     <row r="339" ht="19" customHeight="1">
       <c r="A339" s="1" t="n">
@@ -19134,6 +20148,9 @@
       <c r="P339" t="n">
         <v>98</v>
       </c>
+      <c r="Q339" t="n">
+        <v>347931710</v>
+      </c>
     </row>
     <row r="340" ht="19" customHeight="1">
       <c r="A340" s="1" t="n">
@@ -19185,6 +20202,9 @@
       </c>
       <c r="P340" t="n">
         <v>106</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>345948072</v>
       </c>
     </row>
     <row r="341" ht="19" customHeight="1">
@@ -19238,6 +20258,9 @@
       <c r="P341" t="n">
         <v>61</v>
       </c>
+      <c r="Q341" t="n">
+        <v>369996636</v>
+      </c>
     </row>
     <row r="342" ht="19" customHeight="1">
       <c r="A342" s="1" t="n">
@@ -19300,6 +20323,9 @@
       <c r="P342" t="n">
         <v>131</v>
       </c>
+      <c r="Q342" t="n">
+        <v>346836290</v>
+      </c>
     </row>
     <row r="343" ht="19" customHeight="1">
       <c r="A343" s="1" t="n">
@@ -19351,6 +20377,9 @@
       </c>
       <c r="P343" t="n">
         <v>135</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>354401976</v>
       </c>
     </row>
     <row r="344" ht="19" customHeight="1">
@@ -19396,6 +20425,9 @@
       <c r="P344" t="n">
         <v>166</v>
       </c>
+      <c r="Q344" t="n">
+        <v>380044140</v>
+      </c>
     </row>
     <row r="345" ht="19" customHeight="1">
       <c r="A345" s="1" t="n">
@@ -19455,6 +20487,9 @@
       </c>
       <c r="P345" t="n">
         <v>85</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>350631612</v>
       </c>
     </row>
     <row r="346" ht="19" customHeight="1">
@@ -19508,6 +20543,9 @@
       <c r="P346" t="n">
         <v>88</v>
       </c>
+      <c r="Q346" t="n">
+        <v>356693206</v>
+      </c>
     </row>
     <row r="347" ht="19" customHeight="1">
       <c r="A347" s="1" t="n">
@@ -19564,6 +20602,9 @@
       <c r="P347" t="n">
         <v>234</v>
       </c>
+      <c r="Q347" t="n">
+        <v>370253242</v>
+      </c>
     </row>
     <row r="348" ht="19" customHeight="1">
       <c r="A348" s="1" t="n">
@@ -19625,6 +20666,9 @@
       </c>
       <c r="P348" t="n">
         <v>148</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>348127806</v>
       </c>
     </row>
     <row r="349" ht="19" customHeight="1">
@@ -19674,6 +20718,9 @@
       <c r="P349" t="n">
         <v>273</v>
       </c>
+      <c r="Q349" t="n">
+        <v>350072302</v>
+      </c>
     </row>
     <row r="350" ht="19" customHeight="1">
       <c r="A350" s="1" t="n">
@@ -19726,6 +20773,9 @@
       <c r="P350" t="n">
         <v>199</v>
       </c>
+      <c r="Q350" t="n">
+        <v>385134230</v>
+      </c>
     </row>
     <row r="351" ht="19" customHeight="1">
       <c r="A351" s="1" t="n">
@@ -19780,6 +20830,9 @@
       <c r="P351" t="n">
         <v>203</v>
       </c>
+      <c r="Q351" t="n">
+        <v>352522568</v>
+      </c>
     </row>
     <row r="352" ht="19" customHeight="1">
       <c r="A352" s="1" t="n">
@@ -19842,6 +20895,9 @@
       <c r="P352" t="n">
         <v>40</v>
       </c>
+      <c r="Q352" t="n">
+        <v>354395754</v>
+      </c>
     </row>
     <row r="353" ht="19" customHeight="1">
       <c r="A353" s="1" t="n">
@@ -19904,6 +20960,9 @@
       <c r="P353" t="n">
         <v>171</v>
       </c>
+      <c r="Q353" t="n">
+        <v>381156802</v>
+      </c>
     </row>
     <row r="354" ht="19" customHeight="1">
       <c r="A354" s="1" t="n">
@@ -19960,6 +21019,9 @@
       <c r="P354" t="n">
         <v>92</v>
       </c>
+      <c r="Q354" t="n">
+        <v>344108040</v>
+      </c>
     </row>
     <row r="355" ht="19" customHeight="1">
       <c r="A355" s="1" t="n">
@@ -20019,6 +21081,9 @@
       </c>
       <c r="P355" t="n">
         <v>79</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>348781408</v>
       </c>
     </row>
     <row r="356" ht="19" customHeight="1">
@@ -20066,6 +21131,9 @@
       <c r="P356" t="n">
         <v>103</v>
       </c>
+      <c r="Q356" t="n">
+        <v>374345806</v>
+      </c>
     </row>
     <row r="357" ht="19" customHeight="1">
       <c r="A357" s="1" t="n">
@@ -20126,6 +21194,9 @@
       <c r="P357" t="n">
         <v>197</v>
       </c>
+      <c r="Q357" t="n">
+        <v>344796788</v>
+      </c>
     </row>
     <row r="358" ht="19" customHeight="1">
       <c r="A358" s="1" t="n">
@@ -20186,6 +21257,9 @@
       <c r="P358" t="n">
         <v>115</v>
       </c>
+      <c r="Q358" t="n">
+        <v>346931426</v>
+      </c>
     </row>
     <row r="359" ht="19" customHeight="1">
       <c r="A359" s="1" t="n">
@@ -20246,6 +21320,9 @@
       <c r="P359" t="n">
         <v>206</v>
       </c>
+      <c r="Q359" t="n">
+        <v>373660982</v>
+      </c>
     </row>
     <row r="360" ht="19" customHeight="1">
       <c r="A360" s="1" t="n">
@@ -20300,6 +21377,9 @@
       <c r="P360" t="n">
         <v>62</v>
       </c>
+      <c r="Q360" t="n">
+        <v>342083742</v>
+      </c>
     </row>
     <row r="361" ht="19" customHeight="1">
       <c r="A361" s="1" t="n">
@@ -20351,6 +21431,9 @@
       </c>
       <c r="P361" t="n">
         <v>208</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>347018184</v>
       </c>
     </row>
     <row r="362" ht="19" customHeight="1">
@@ -20396,6 +21479,9 @@
       <c r="P362" t="n">
         <v>90</v>
       </c>
+      <c r="Q362" t="n">
+        <v>354933898</v>
+      </c>
     </row>
     <row r="363" ht="19" customHeight="1">
       <c r="A363" s="1" t="n">
@@ -20450,6 +21536,9 @@
       <c r="P363" t="n">
         <v>139</v>
       </c>
+      <c r="Q363" t="n">
+        <v>323582976</v>
+      </c>
     </row>
     <row r="364" ht="19" customHeight="1">
       <c r="A364" s="1" t="n">
@@ -20510,6 +21599,9 @@
       <c r="P364" t="n">
         <v>72</v>
       </c>
+      <c r="Q364" t="n">
+        <v>343699030</v>
+      </c>
     </row>
     <row r="365" ht="19" customHeight="1">
       <c r="A365" s="1" t="n">
@@ -20564,6 +21656,9 @@
       <c r="P365" t="n">
         <v>69</v>
       </c>
+      <c r="Q365" t="n">
+        <v>368550846</v>
+      </c>
     </row>
     <row r="366" ht="19" customHeight="1">
       <c r="A366" s="1" t="n">
@@ -20623,6 +21718,9 @@
       </c>
       <c r="P366" t="n">
         <v>178</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>339434250</v>
       </c>
     </row>
     <row r="367" ht="19" customHeight="1">
@@ -20668,6 +21766,9 @@
       <c r="P367" t="n">
         <v>163</v>
       </c>
+      <c r="Q367" t="n">
+        <v>348744958</v>
+      </c>
     </row>
     <row r="368" ht="19" customHeight="1">
       <c r="A368" s="1" t="n">
@@ -20724,6 +21825,9 @@
       <c r="P368" t="n">
         <v>65</v>
       </c>
+      <c r="Q368" t="n">
+        <v>377101508</v>
+      </c>
     </row>
     <row r="369" ht="19" customHeight="1">
       <c r="A369" s="1" t="n">
@@ -20775,6 +21879,9 @@
       </c>
       <c r="P369" t="n">
         <v>250</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>354097454</v>
       </c>
     </row>
     <row r="370" ht="19" customHeight="1">
@@ -20830,6 +21937,9 @@
       <c r="P370" t="n">
         <v>178</v>
       </c>
+      <c r="Q370" t="n">
+        <v>341744330</v>
+      </c>
     </row>
     <row r="371" ht="19" customHeight="1">
       <c r="A371" s="1" t="n">
@@ -20886,6 +21996,9 @@
       <c r="P371" t="n">
         <v>66</v>
       </c>
+      <c r="Q371" t="n">
+        <v>352746618</v>
+      </c>
     </row>
     <row r="372" ht="19" customHeight="1">
       <c r="A372" s="1" t="n">
@@ -20937,6 +22050,9 @@
       </c>
       <c r="P372" t="n">
         <v>113</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>376451952</v>
       </c>
     </row>
     <row r="373" ht="19" customHeight="1">
@@ -20990,6 +22106,9 @@
       <c r="P373" t="n">
         <v>64</v>
       </c>
+      <c r="Q373" t="n">
+        <v>342882326</v>
+      </c>
     </row>
     <row r="374" ht="19" customHeight="1">
       <c r="A374" s="1" t="n">
@@ -21050,6 +22169,9 @@
       <c r="P374" t="n">
         <v>72</v>
       </c>
+      <c r="Q374" t="n">
+        <v>343140726</v>
+      </c>
     </row>
     <row r="375" ht="19" customHeight="1">
       <c r="A375" s="1" t="n">
@@ -21106,6 +22228,9 @@
       <c r="P375" t="n">
         <v>183</v>
       </c>
+      <c r="Q375" t="n">
+        <v>364140764</v>
+      </c>
     </row>
     <row r="376" ht="19" customHeight="1">
       <c r="A376" s="1" t="n">
@@ -21160,6 +22285,9 @@
       <c r="P376" t="n">
         <v>68</v>
       </c>
+      <c r="Q376" t="n">
+        <v>341159894</v>
+      </c>
     </row>
     <row r="377" ht="19" customHeight="1">
       <c r="A377" s="1" t="n">
@@ -21219,6 +22347,9 @@
       </c>
       <c r="P377" t="n">
         <v>228</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>352551896</v>
       </c>
     </row>
     <row r="378" ht="19" customHeight="1">
@@ -21268,6 +22399,9 @@
       <c r="P378" t="n">
         <v>84</v>
       </c>
+      <c r="Q378" t="n">
+        <v>375813786</v>
+      </c>
     </row>
     <row r="379" ht="19" customHeight="1">
       <c r="A379" s="1" t="n">
@@ -21329,6 +22463,9 @@
       </c>
       <c r="P379" t="n">
         <v>80</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>346613892</v>
       </c>
     </row>
     <row r="380" ht="19" customHeight="1">
@@ -21374,6 +22511,9 @@
       <c r="P380" t="n">
         <v>419</v>
       </c>
+      <c r="Q380" t="n">
+        <v>351905686</v>
+      </c>
     </row>
     <row r="381" ht="19" customHeight="1">
       <c r="A381" s="1" t="n">
@@ -21435,6 +22575,9 @@
       </c>
       <c r="P381" t="n">
         <v>69</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>473613616</v>
       </c>
     </row>
     <row r="382" ht="19" customHeight="1">
@@ -21484,6 +22627,9 @@
       <c r="P382" t="n">
         <v>165</v>
       </c>
+      <c r="Q382" t="n">
+        <v>438566712</v>
+      </c>
     </row>
     <row r="383" ht="19" customHeight="1">
       <c r="A383" s="1" t="n">
@@ -21538,6 +22684,9 @@
       <c r="P383" t="n">
         <v>118</v>
       </c>
+      <c r="Q383" t="n">
+        <v>445426800</v>
+      </c>
     </row>
     <row r="384" ht="19" customHeight="1">
       <c r="A384" s="1" t="n">
@@ -21597,6 +22746,9 @@
       </c>
       <c r="P384" t="n">
         <v>120</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>479114118</v>
       </c>
     </row>
     <row r="385" ht="19" customHeight="1">
@@ -21644,6 +22796,9 @@
       <c r="P385" t="n">
         <v>135</v>
       </c>
+      <c r="Q385" t="n">
+        <v>439889754</v>
+      </c>
     </row>
     <row r="386" ht="19" customHeight="1">
       <c r="A386" s="1" t="n">
@@ -21699,6 +22854,9 @@
       </c>
       <c r="P386" t="n">
         <v>236</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>435463406</v>
       </c>
     </row>
     <row r="387" ht="19" customHeight="1">
@@ -21752,6 +22910,9 @@
       <c r="P387" t="n">
         <v>87</v>
       </c>
+      <c r="Q387" t="n">
+        <v>471463176</v>
+      </c>
     </row>
     <row r="388" ht="19" customHeight="1">
       <c r="A388" s="1" t="n">
@@ -21805,6 +22966,9 @@
       </c>
       <c r="P388" t="n">
         <v>128</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>432267736</v>
       </c>
     </row>
     <row r="389" ht="19" customHeight="1">
@@ -21846,6 +23010,9 @@
       <c r="P389" t="n">
         <v>103</v>
       </c>
+      <c r="Q389" t="n">
+        <v>439880754</v>
+      </c>
     </row>
     <row r="390" ht="19" customHeight="1">
       <c r="A390" s="1" t="n">
@@ -21906,6 +23073,9 @@
       <c r="P390" t="n">
         <v>256</v>
       </c>
+      <c r="Q390" t="n">
+        <v>465732500</v>
+      </c>
     </row>
     <row r="391" ht="19" customHeight="1">
       <c r="A391" s="1" t="n">
@@ -21966,6 +23136,9 @@
       <c r="P391" t="n">
         <v>131</v>
       </c>
+      <c r="Q391" t="n">
+        <v>429233698</v>
+      </c>
     </row>
     <row r="392" ht="19" customHeight="1">
       <c r="A392" s="1" t="n">
@@ -22026,6 +23199,9 @@
       <c r="P392" t="n">
         <v>855</v>
       </c>
+      <c r="Q392" t="n">
+        <v>446966366</v>
+      </c>
     </row>
     <row r="393" ht="19" customHeight="1">
       <c r="A393" s="1" t="n">
@@ -22085,6 +23261,9 @@
       </c>
       <c r="P393" t="n">
         <v>307</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>491074898</v>
       </c>
     </row>
     <row r="394" ht="19" customHeight="1">
@@ -22134,6 +23313,9 @@
       <c r="P394" t="n">
         <v>97</v>
       </c>
+      <c r="Q394" t="n">
+        <v>456605906</v>
+      </c>
     </row>
     <row r="395" ht="19" customHeight="1">
       <c r="A395" s="1" t="n">
@@ -22193,6 +23375,9 @@
       </c>
       <c r="P395" t="n">
         <v>180</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>459136590</v>
       </c>
     </row>
     <row r="396" ht="19" customHeight="1">
@@ -22246,6 +23431,9 @@
       <c r="P396" t="n">
         <v>188</v>
       </c>
+      <c r="Q396" t="n">
+        <v>481535824</v>
+      </c>
     </row>
     <row r="397" ht="19" customHeight="1">
       <c r="A397" s="1" t="n">
@@ -22294,6 +23482,9 @@
       <c r="P397" t="n">
         <v>178</v>
       </c>
+      <c r="Q397" t="n">
+        <v>441190576</v>
+      </c>
     </row>
     <row r="398" ht="19" customHeight="1">
       <c r="A398" s="1" t="n">
@@ -22346,6 +23537,9 @@
       <c r="P398" t="n">
         <v>226</v>
       </c>
+      <c r="Q398" t="n">
+        <v>463226948</v>
+      </c>
     </row>
     <row r="399" ht="19" customHeight="1">
       <c r="A399" s="1" t="n">
@@ -22400,6 +23594,9 @@
       <c r="P399" t="n">
         <v>315</v>
       </c>
+      <c r="Q399" t="n">
+        <v>491869822</v>
+      </c>
     </row>
     <row r="400" ht="19" customHeight="1">
       <c r="A400" s="1" t="n">
@@ -22460,6 +23657,9 @@
       <c r="P400" t="n">
         <v>121</v>
       </c>
+      <c r="Q400" t="n">
+        <v>451419346</v>
+      </c>
     </row>
     <row r="401" ht="19" customHeight="1">
       <c r="A401" s="1" t="n">
@@ -22512,6 +23712,9 @@
       <c r="P401" t="n">
         <v>358</v>
       </c>
+      <c r="Q401" t="n">
+        <v>413166618</v>
+      </c>
     </row>
     <row r="402" ht="19" customHeight="1">
       <c r="A402" s="1" t="n">
@@ -22564,6 +23767,9 @@
       <c r="P402" t="n">
         <v>120</v>
       </c>
+      <c r="Q402" t="n">
+        <v>438660552</v>
+      </c>
     </row>
     <row r="403" ht="19" customHeight="1">
       <c r="A403" s="1" t="n">
@@ -22625,6 +23831,9 @@
       </c>
       <c r="P403" t="n">
         <v>85</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>412346050</v>
       </c>
     </row>
     <row r="404" ht="19" customHeight="1">
@@ -22678,6 +23887,9 @@
       <c r="P404" t="n">
         <v>133</v>
       </c>
+      <c r="Q404" t="n">
+        <v>411127632</v>
+      </c>
     </row>
     <row r="405" ht="19" customHeight="1">
       <c r="A405" s="1" t="n">
@@ -22738,6 +23950,9 @@
       <c r="P405" t="n">
         <v>63</v>
       </c>
+      <c r="Q405" t="n">
+        <v>434694410</v>
+      </c>
     </row>
     <row r="406" ht="19" customHeight="1">
       <c r="A406" s="1" t="n">
@@ -22790,6 +24005,9 @@
       <c r="P406" t="n">
         <v>193</v>
       </c>
+      <c r="Q406" t="n">
+        <v>428356574</v>
+      </c>
     </row>
     <row r="407" ht="19" customHeight="1">
       <c r="A407" s="1" t="n">
@@ -22846,6 +24064,9 @@
       <c r="P407" t="n">
         <v>204</v>
       </c>
+      <c r="Q407" t="n">
+        <v>404437376</v>
+      </c>
     </row>
     <row r="408" ht="19" customHeight="1">
       <c r="A408" s="1" t="n">
@@ -22906,6 +24127,9 @@
       <c r="P408" t="n">
         <v>116</v>
       </c>
+      <c r="Q408" t="n">
+        <v>439670530</v>
+      </c>
     </row>
     <row r="409" ht="19" customHeight="1">
       <c r="A409" s="1" t="n">
@@ -22966,6 +24190,9 @@
       <c r="P409" t="n">
         <v>135</v>
       </c>
+      <c r="Q409" t="n">
+        <v>396515706</v>
+      </c>
     </row>
     <row r="410" ht="19" customHeight="1">
       <c r="A410" s="1" t="n">
@@ -23018,6 +24245,9 @@
       <c r="P410" t="n">
         <v>118</v>
       </c>
+      <c r="Q410" t="n">
+        <v>391221400</v>
+      </c>
     </row>
     <row r="411" ht="19" customHeight="1">
       <c r="A411" s="1" t="n">
@@ -23078,6 +24308,9 @@
       <c r="P411" t="n">
         <v>139</v>
       </c>
+      <c r="Q411" t="n">
+        <v>424386010</v>
+      </c>
     </row>
     <row r="412" ht="19" customHeight="1">
       <c r="A412" s="1" t="n">
@@ -23134,6 +24367,9 @@
       <c r="P412" t="n">
         <v>328</v>
       </c>
+      <c r="Q412" t="n">
+        <v>388340672</v>
+      </c>
     </row>
     <row r="413" ht="19" customHeight="1">
       <c r="A413" s="1" t="n">
@@ -23195,6 +24431,9 @@
       </c>
       <c r="P413" t="n">
         <v>113</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>388819806</v>
       </c>
     </row>
     <row r="414" ht="19" customHeight="1">
@@ -23248,6 +24487,9 @@
       <c r="P414" t="n">
         <v>155</v>
       </c>
+      <c r="Q414" t="n">
+        <v>419205612</v>
+      </c>
     </row>
     <row r="415" ht="19" customHeight="1">
       <c r="A415" s="1" t="n">
@@ -23308,6 +24550,9 @@
       <c r="P415" t="n">
         <v>334</v>
       </c>
+      <c r="Q415" t="n">
+        <v>375791606</v>
+      </c>
     </row>
     <row r="416" ht="19" customHeight="1">
       <c r="A416" s="1" t="n">
@@ -23367,6 +24612,9 @@
       </c>
       <c r="P416" t="n">
         <v>129</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>385376562</v>
       </c>
     </row>
     <row r="417" ht="19" customHeight="1">
@@ -23414,6 +24662,9 @@
       <c r="P417" t="n">
         <v>202</v>
       </c>
+      <c r="Q417" t="n">
+        <v>460490078</v>
+      </c>
     </row>
     <row r="418" ht="19" customHeight="1">
       <c r="A418" s="1" t="n">
@@ -23466,6 +24717,9 @@
       <c r="P418" t="n">
         <v>132</v>
       </c>
+      <c r="Q418" t="n">
+        <v>384392632</v>
+      </c>
     </row>
     <row r="419" ht="19" customHeight="1">
       <c r="A419" s="1" t="n">
@@ -23522,6 +24776,9 @@
       <c r="P419" t="n">
         <v>124</v>
       </c>
+      <c r="Q419" t="n">
+        <v>400862420</v>
+      </c>
     </row>
     <row r="420" ht="19" customHeight="1">
       <c r="A420" s="1" t="n">
@@ -23578,6 +24835,9 @@
       <c r="P420" t="n">
         <v>111</v>
       </c>
+      <c r="Q420" t="n">
+        <v>376048608</v>
+      </c>
     </row>
     <row r="421" ht="19" customHeight="1">
       <c r="A421" s="1" t="n">
@@ -23634,6 +24894,9 @@
       <c r="P421" t="n">
         <v>344</v>
       </c>
+      <c r="Q421" t="n">
+        <v>381850646</v>
+      </c>
     </row>
     <row r="422" ht="19" customHeight="1">
       <c r="A422" s="1" t="n">
@@ -23690,6 +24953,9 @@
       <c r="P422" t="n">
         <v>162</v>
       </c>
+      <c r="Q422" t="n">
+        <v>422332862</v>
+      </c>
     </row>
     <row r="423" ht="19" customHeight="1">
       <c r="A423" s="1" t="n">
@@ -23752,6 +25018,9 @@
       <c r="P423" t="n">
         <v>115</v>
       </c>
+      <c r="Q423" t="n">
+        <v>385907866</v>
+      </c>
     </row>
     <row r="424" ht="19" customHeight="1">
       <c r="A424" s="1" t="n">
@@ -23814,6 +25083,9 @@
       <c r="P424" t="n">
         <v>149</v>
       </c>
+      <c r="Q424" t="n">
+        <v>389691430</v>
+      </c>
     </row>
     <row r="425" ht="19" customHeight="1">
       <c r="A425" s="1" t="n">
@@ -23874,6 +25146,9 @@
       <c r="P425" t="n">
         <v>168</v>
       </c>
+      <c r="Q425" t="n">
+        <v>426478858</v>
+      </c>
     </row>
     <row r="426" ht="19" customHeight="1">
       <c r="A426" s="1" t="n">
@@ -23926,6 +25201,9 @@
       <c r="P426" t="n">
         <v>317</v>
       </c>
+      <c r="Q426" t="n">
+        <v>397475096</v>
+      </c>
     </row>
     <row r="427" ht="19" customHeight="1">
       <c r="A427" s="1" t="n">
@@ -23986,6 +25264,9 @@
       <c r="P427" t="n">
         <v>226</v>
       </c>
+      <c r="Q427" t="n">
+        <v>406699544</v>
+      </c>
     </row>
     <row r="428" ht="19" customHeight="1">
       <c r="A428" s="1" t="n">
@@ -24046,6 +25327,9 @@
       <c r="P428" t="n">
         <v>80</v>
       </c>
+      <c r="Q428" t="n">
+        <v>439339144</v>
+      </c>
     </row>
     <row r="429" ht="19" customHeight="1">
       <c r="A429" s="1" t="n">
@@ -24102,6 +25386,9 @@
       <c r="P429" t="n">
         <v>169</v>
       </c>
+      <c r="Q429" t="n">
+        <v>386827864</v>
+      </c>
     </row>
     <row r="430" ht="19" customHeight="1">
       <c r="A430" s="1" t="n">
@@ -24158,6 +25445,9 @@
       <c r="P430" t="n">
         <v>169</v>
       </c>
+      <c r="Q430" t="n">
+        <v>390568100</v>
+      </c>
     </row>
     <row r="431" ht="19" customHeight="1">
       <c r="A431" s="1" t="n">
@@ -24210,6 +25500,9 @@
       <c r="P431" t="n">
         <v>91</v>
       </c>
+      <c r="Q431" t="n">
+        <v>429174194</v>
+      </c>
     </row>
     <row r="432" ht="19" customHeight="1">
       <c r="A432" s="1" t="n">
@@ -24270,6 +25563,9 @@
       <c r="P432" t="n">
         <v>66</v>
       </c>
+      <c r="Q432" t="n">
+        <v>392951650</v>
+      </c>
     </row>
     <row r="433" ht="19" customHeight="1">
       <c r="A433" s="1" t="n">
@@ -24326,6 +25622,9 @@
       <c r="P433" t="n">
         <v>211</v>
       </c>
+      <c r="Q433" t="n">
+        <v>394720204</v>
+      </c>
     </row>
     <row r="434" ht="19" customHeight="1">
       <c r="A434" s="1" t="n">
@@ -24386,6 +25685,9 @@
       <c r="P434" t="n">
         <v>154</v>
       </c>
+      <c r="Q434" t="n">
+        <v>417970572</v>
+      </c>
     </row>
     <row r="435" ht="19" customHeight="1">
       <c r="A435" s="1" t="n">
@@ -24447,6 +25749,9 @@
       </c>
       <c r="P435" t="n">
         <v>146</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>393060268</v>
       </c>
     </row>
     <row r="436" ht="19" customHeight="1">
@@ -24502,6 +25807,9 @@
       <c r="P436" t="n">
         <v>113</v>
       </c>
+      <c r="Q436" t="n">
+        <v>395500258</v>
+      </c>
     </row>
     <row r="437" ht="19" customHeight="1">
       <c r="A437" s="1" t="n">
@@ -24561,6 +25869,9 @@
       </c>
       <c r="P437" t="n">
         <v>186</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>419594048</v>
       </c>
     </row>
     <row r="438" ht="19" customHeight="1">
@@ -24606,6 +25917,9 @@
       <c r="P438" t="n">
         <v>227</v>
       </c>
+      <c r="Q438" t="n">
+        <v>374535064</v>
+      </c>
     </row>
     <row r="439" ht="19" customHeight="1">
       <c r="A439" s="1" t="n">
@@ -24666,6 +25980,9 @@
       <c r="P439" t="n">
         <v>101</v>
       </c>
+      <c r="Q439" t="n">
+        <v>379779720</v>
+      </c>
     </row>
     <row r="440" ht="19" customHeight="1">
       <c r="A440" s="1" t="n">
@@ -24728,6 +26045,9 @@
       <c r="P440" t="n">
         <v>163</v>
       </c>
+      <c r="Q440" t="n">
+        <v>400660020</v>
+      </c>
     </row>
     <row r="441" ht="19" customHeight="1">
       <c r="A441" s="1" t="n">
@@ -24779,6 +26099,9 @@
       </c>
       <c r="P441" t="n">
         <v>141</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>375726786</v>
       </c>
     </row>
     <row r="442" ht="19" customHeight="1">
@@ -24824,6 +26147,9 @@
       <c r="P442" t="n">
         <v>82</v>
       </c>
+      <c r="Q442" t="n">
+        <v>372292440</v>
+      </c>
     </row>
     <row r="443" ht="19" customHeight="1">
       <c r="A443" s="1" t="n">
@@ -24884,6 +26210,9 @@
       <c r="P443" t="n">
         <v>160</v>
       </c>
+      <c r="Q443" t="n">
+        <v>406066676</v>
+      </c>
     </row>
     <row r="444" ht="19" customHeight="1">
       <c r="A444" s="1" t="n">
@@ -24945,6 +26274,9 @@
       </c>
       <c r="P444" t="n">
         <v>119</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>378571560</v>
       </c>
     </row>
     <row r="445" ht="19" customHeight="1">
@@ -24990,6 +26322,9 @@
       <c r="P445" t="n">
         <v>111</v>
       </c>
+      <c r="Q445" t="n">
+        <v>381434232</v>
+      </c>
     </row>
     <row r="446" ht="19" customHeight="1">
       <c r="A446" s="1" t="n">
@@ -25043,6 +26378,9 @@
       </c>
       <c r="P446" t="n">
         <v>170</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>399308858</v>
       </c>
     </row>
     <row r="447" ht="19" customHeight="1">
@@ -25090,6 +26428,9 @@
       <c r="P447" t="n">
         <v>114</v>
       </c>
+      <c r="Q447" t="n">
+        <v>377141604</v>
+      </c>
     </row>
     <row r="448" ht="19" customHeight="1">
       <c r="A448" s="1" t="n">
@@ -25142,6 +26483,9 @@
       <c r="P448" t="n">
         <v>169</v>
       </c>
+      <c r="Q448" t="n">
+        <v>385795918</v>
+      </c>
     </row>
     <row r="449" ht="19" customHeight="1">
       <c r="A449" s="1" t="n">
@@ -25202,6 +26546,9 @@
       <c r="P449" t="n">
         <v>133</v>
       </c>
+      <c r="Q449" t="n">
+        <v>409814910</v>
+      </c>
     </row>
     <row r="450" ht="19" customHeight="1">
       <c r="A450" s="1" t="n">
@@ -25262,6 +26609,9 @@
       <c r="P450" t="n">
         <v>123</v>
       </c>
+      <c r="Q450" t="n">
+        <v>373270898</v>
+      </c>
     </row>
     <row r="451" ht="19" customHeight="1">
       <c r="A451" s="1" t="n">
@@ -25316,6 +26666,9 @@
       <c r="P451" t="n">
         <v>68</v>
       </c>
+      <c r="Q451" t="n">
+        <v>373242104</v>
+      </c>
     </row>
     <row r="452" ht="19" customHeight="1">
       <c r="A452" s="1" t="n">
@@ -25378,6 +26731,9 @@
       <c r="P452" t="n">
         <v>77</v>
       </c>
+      <c r="Q452" t="n">
+        <v>399679256</v>
+      </c>
     </row>
     <row r="453" ht="19" customHeight="1">
       <c r="A453" s="1" t="n">
@@ -25434,6 +26790,9 @@
       <c r="P453" t="n">
         <v>174</v>
       </c>
+      <c r="Q453" t="n">
+        <v>364051920</v>
+      </c>
     </row>
     <row r="454" ht="19" customHeight="1">
       <c r="A454" s="1" t="n">
@@ -25496,6 +26855,9 @@
       <c r="P454" t="n">
         <v>57</v>
       </c>
+      <c r="Q454" t="n">
+        <v>326832578</v>
+      </c>
     </row>
     <row r="455" ht="19" customHeight="1">
       <c r="A455" s="1" t="n">
@@ -25548,6 +26910,9 @@
       <c r="P455" t="n">
         <v>130</v>
       </c>
+      <c r="Q455" t="n">
+        <v>359533236</v>
+      </c>
     </row>
     <row r="456" ht="19" customHeight="1">
       <c r="A456" s="1" t="n">
@@ -25600,6 +26965,9 @@
       <c r="P456" t="n">
         <v>140</v>
       </c>
+      <c r="Q456" t="n">
+        <v>366315720</v>
+      </c>
     </row>
     <row r="457" ht="19" customHeight="1">
       <c r="A457" s="1" t="n">
@@ -25660,6 +27028,9 @@
       <c r="P457" t="n">
         <v>194</v>
       </c>
+      <c r="Q457" t="n">
+        <v>365959336</v>
+      </c>
     </row>
     <row r="458" ht="19" customHeight="1">
       <c r="A458" s="1" t="n">
@@ -25720,6 +27091,9 @@
       <c r="P458" t="n">
         <v>161</v>
       </c>
+      <c r="Q458" t="n">
+        <v>390015600</v>
+      </c>
     </row>
     <row r="459" ht="19" customHeight="1">
       <c r="A459" s="1" t="n">
@@ -25782,6 +27156,9 @@
       <c r="P459" t="n">
         <v>100</v>
       </c>
+      <c r="Q459" t="n">
+        <v>367998390</v>
+      </c>
     </row>
     <row r="460" ht="19" customHeight="1">
       <c r="A460" s="1" t="n">
@@ -25834,6 +27211,9 @@
       <c r="P460" t="n">
         <v>176</v>
       </c>
+      <c r="Q460" t="n">
+        <v>374131396</v>
+      </c>
     </row>
     <row r="461" ht="19" customHeight="1">
       <c r="A461" s="1" t="n">
@@ -25888,6 +27268,9 @@
       <c r="P461" t="n">
         <v>67</v>
       </c>
+      <c r="Q461" t="n">
+        <v>396605082</v>
+      </c>
     </row>
     <row r="462" ht="19" customHeight="1">
       <c r="A462" s="1" t="n">
@@ -25948,6 +27331,9 @@
       <c r="P462" t="n">
         <v>81</v>
       </c>
+      <c r="Q462" t="n">
+        <v>366700300</v>
+      </c>
     </row>
     <row r="463" ht="19" customHeight="1">
       <c r="A463" s="1" t="n">
@@ -26004,6 +27390,9 @@
       <c r="P463" t="n">
         <v>869</v>
       </c>
+      <c r="Q463" t="n">
+        <v>362960216</v>
+      </c>
     </row>
     <row r="464" ht="19" customHeight="1">
       <c r="A464" s="1" t="n">
@@ -26064,6 +27453,9 @@
       <c r="P464" t="n">
         <v>225</v>
       </c>
+      <c r="Q464" t="n">
+        <v>393500536</v>
+      </c>
     </row>
     <row r="465" ht="19" customHeight="1">
       <c r="A465" s="1" t="n">
@@ -26123,6 +27515,9 @@
       </c>
       <c r="P465" t="n">
         <v>220</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>357078086</v>
       </c>
     </row>
     <row r="466" ht="19" customHeight="1">
@@ -26172,6 +27567,9 @@
       <c r="P466" t="n">
         <v>149</v>
       </c>
+      <c r="Q466" t="n">
+        <v>358070626</v>
+      </c>
     </row>
     <row r="467" ht="19" customHeight="1">
       <c r="A467" s="1" t="n">
@@ -26224,6 +27622,9 @@
       <c r="P467" t="n">
         <v>134</v>
       </c>
+      <c r="Q467" t="n">
+        <v>366761624</v>
+      </c>
     </row>
     <row r="468" ht="19" customHeight="1">
       <c r="A468" s="1" t="n">
@@ -26278,6 +27679,9 @@
       <c r="P468" t="n">
         <v>115</v>
       </c>
+      <c r="Q468" t="n">
+        <v>353685018</v>
+      </c>
     </row>
     <row r="469" ht="19" customHeight="1">
       <c r="A469" s="1" t="n">
@@ -26334,6 +27738,9 @@
       <c r="P469" t="n">
         <v>77</v>
       </c>
+      <c r="Q469" t="n">
+        <v>366105242</v>
+      </c>
     </row>
     <row r="470" ht="19" customHeight="1">
       <c r="A470" s="1" t="n">
@@ -26388,6 +27795,9 @@
       <c r="P470" t="n">
         <v>133</v>
       </c>
+      <c r="Q470" t="n">
+        <v>389225746</v>
+      </c>
     </row>
     <row r="471" ht="19" customHeight="1">
       <c r="A471" s="1" t="n">
@@ -26449,6 +27859,9 @@
       </c>
       <c r="P471" t="n">
         <v>106</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>357848508</v>
       </c>
     </row>
     <row r="472" ht="19" customHeight="1">
@@ -26502,6 +27915,9 @@
       <c r="P472" t="n">
         <v>94</v>
       </c>
+      <c r="Q472" t="n">
+        <v>366359214</v>
+      </c>
     </row>
     <row r="473" ht="19" customHeight="1">
       <c r="A473" s="1" t="n">
@@ -26553,6 +27969,9 @@
       </c>
       <c r="P473" t="n">
         <v>157</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>389127714</v>
       </c>
     </row>
     <row r="474" ht="19" customHeight="1">
@@ -26607,6 +28026,9 @@
       </c>
       <c r="P474" t="n">
         <v>291</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>356576372</v>
       </c>
     </row>
     <row r="475" ht="19" customHeight="1">
@@ -26652,6 +28074,9 @@
       <c r="P475" t="n">
         <v>93</v>
       </c>
+      <c r="Q475" t="n">
+        <v>367456356</v>
+      </c>
     </row>
     <row r="476" ht="19" customHeight="1">
       <c r="A476" s="1" t="n">
@@ -26711,6 +28136,9 @@
       </c>
       <c r="P476" t="n">
         <v>219</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>388014508</v>
       </c>
     </row>
     <row r="477" ht="19" customHeight="1">
@@ -26760,6 +28188,9 @@
       <c r="P477" t="n">
         <v>110</v>
       </c>
+      <c r="Q477" t="n">
+        <v>357410052</v>
+      </c>
     </row>
     <row r="478" ht="19" customHeight="1">
       <c r="A478" s="1" t="n">
@@ -26812,6 +28243,9 @@
       <c r="P478" t="n">
         <v>121</v>
       </c>
+      <c r="Q478" t="n">
+        <v>359396990</v>
+      </c>
     </row>
     <row r="479" ht="19" customHeight="1">
       <c r="A479" s="1" t="n">
@@ -26866,6 +28300,9 @@
       <c r="P479" t="n">
         <v>164</v>
       </c>
+      <c r="Q479" t="n">
+        <v>388648778</v>
+      </c>
     </row>
     <row r="480" ht="19" customHeight="1">
       <c r="A480" s="1" t="n">
@@ -26926,6 +28363,9 @@
       <c r="P480" t="n">
         <v>78</v>
       </c>
+      <c r="Q480" t="n">
+        <v>357617458</v>
+      </c>
     </row>
     <row r="481" ht="19" customHeight="1">
       <c r="A481" s="1" t="n">
@@ -26988,6 +28428,9 @@
       <c r="P481" t="n">
         <v>175</v>
       </c>
+      <c r="Q481" t="n">
+        <v>356433094</v>
+      </c>
     </row>
     <row r="482" ht="19" customHeight="1">
       <c r="A482" s="1" t="n">
@@ -27041,6 +28484,9 @@
       </c>
       <c r="P482" t="n">
         <v>189</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>380376886</v>
       </c>
     </row>
     <row r="483" ht="19" customHeight="1">
@@ -27090,6 +28536,9 @@
       <c r="P483" t="n">
         <v>153</v>
       </c>
+      <c r="Q483" t="n">
+        <v>354913968</v>
+      </c>
     </row>
     <row r="484" ht="19" customHeight="1">
       <c r="A484" s="1" t="n">
@@ -27142,6 +28591,9 @@
       <c r="P484" t="n">
         <v>111</v>
       </c>
+      <c r="Q484" t="n">
+        <v>350559496</v>
+      </c>
     </row>
     <row r="485" ht="19" customHeight="1">
       <c r="A485" s="1" t="n">
@@ -27196,6 +28648,9 @@
       <c r="P485" t="n">
         <v>107</v>
       </c>
+      <c r="Q485" t="n">
+        <v>380647944</v>
+      </c>
     </row>
     <row r="486" ht="19" customHeight="1">
       <c r="A486" s="1" t="n">
@@ -27248,6 +28703,9 @@
       <c r="P486" t="n">
         <v>180</v>
       </c>
+      <c r="Q486" t="n">
+        <v>350614738</v>
+      </c>
     </row>
     <row r="487" ht="19" customHeight="1">
       <c r="A487" s="1" t="n">
@@ -27300,6 +28758,9 @@
       <c r="P487" t="n">
         <v>149</v>
       </c>
+      <c r="Q487" t="n">
+        <v>353894972</v>
+      </c>
     </row>
     <row r="488" ht="19" customHeight="1">
       <c r="A488" s="1" t="n">
@@ -27360,6 +28821,9 @@
       <c r="P488" t="n">
         <v>120</v>
       </c>
+      <c r="Q488" t="n">
+        <v>378156970</v>
+      </c>
     </row>
     <row r="489" ht="19" customHeight="1">
       <c r="A489" s="1" t="n">
@@ -27416,6 +28880,9 @@
       <c r="P489" t="n">
         <v>145</v>
       </c>
+      <c r="Q489" t="n">
+        <v>352801672</v>
+      </c>
     </row>
     <row r="490" ht="19" customHeight="1">
       <c r="A490" s="1" t="n">
@@ -27468,6 +28935,9 @@
       <c r="P490" t="n">
         <v>120</v>
       </c>
+      <c r="Q490" t="n">
+        <v>350903250</v>
+      </c>
     </row>
     <row r="491" ht="19" customHeight="1">
       <c r="A491" s="1" t="n">
@@ -27529,6 +28999,9 @@
       </c>
       <c r="P491" t="n">
         <v>93</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>373432674</v>
       </c>
     </row>
     <row r="492" ht="19" customHeight="1">
@@ -27574,6 +29047,9 @@
       <c r="P492" t="n">
         <v>118</v>
       </c>
+      <c r="Q492" t="n">
+        <v>345276906</v>
+      </c>
     </row>
     <row r="493" ht="19" customHeight="1">
       <c r="A493" s="1" t="n">
@@ -27635,6 +29111,9 @@
       </c>
       <c r="P493" t="n">
         <v>105</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>350994188</v>
       </c>
     </row>
     <row r="494" ht="19" customHeight="1">
@@ -27684,6 +29163,9 @@
       <c r="P494" t="n">
         <v>68</v>
       </c>
+      <c r="Q494" t="n">
+        <v>378870024</v>
+      </c>
     </row>
     <row r="495" ht="19" customHeight="1">
       <c r="A495" s="1" t="n">
@@ -27736,6 +29218,9 @@
       <c r="P495" t="n">
         <v>82</v>
       </c>
+      <c r="Q495" t="n">
+        <v>346126366</v>
+      </c>
     </row>
     <row r="496" ht="19" customHeight="1">
       <c r="A496" s="1" t="n">
@@ -27796,6 +29281,9 @@
       <c r="P496" t="n">
         <v>197</v>
       </c>
+      <c r="Q496" t="n">
+        <v>358843770</v>
+      </c>
     </row>
     <row r="497" ht="19" customHeight="1">
       <c r="A497" s="1" t="n">
@@ -27856,6 +29344,9 @@
       <c r="P497" t="n">
         <v>114</v>
       </c>
+      <c r="Q497" t="n">
+        <v>381527438</v>
+      </c>
     </row>
     <row r="498" ht="19" customHeight="1">
       <c r="A498" s="1" t="n">
@@ -27915,6 +29406,9 @@
       </c>
       <c r="P498" t="n">
         <v>110</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>350909082</v>
       </c>
     </row>
     <row r="499" ht="19" customHeight="1">
@@ -27970,6 +29464,9 @@
       <c r="P499" t="n">
         <v>136</v>
       </c>
+      <c r="Q499" t="n">
+        <v>356349402</v>
+      </c>
     </row>
     <row r="500" ht="19" customHeight="1">
       <c r="A500" s="1" t="n">
@@ -28022,6 +29519,9 @@
       <c r="P500" t="n">
         <v>196</v>
       </c>
+      <c r="Q500" t="n">
+        <v>378464962</v>
+      </c>
     </row>
     <row r="501" ht="19" customHeight="1">
       <c r="A501" s="5" t="n">
@@ -28082,6 +29582,9 @@
       <c r="P501" t="n">
         <v>78</v>
       </c>
+      <c r="Q501" t="n">
+        <v>347483168</v>
+      </c>
     </row>
     <row r="502" ht="19" customHeight="1">
       <c r="A502" s="8" t="n">
@@ -28142,6 +29645,9 @@
       <c r="P502" t="n">
         <v>165</v>
       </c>
+      <c r="Q502" t="n">
+        <v>350353036</v>
+      </c>
     </row>
     <row r="503" ht="19" customHeight="1">
       <c r="A503" s="11" t="n">
@@ -28194,6 +29700,9 @@
       <c r="P503" t="n">
         <v>178</v>
       </c>
+      <c r="Q503" t="n">
+        <v>380958632</v>
+      </c>
     </row>
     <row r="504" ht="19" customHeight="1">
       <c r="A504" s="1" t="n">
@@ -28253,6 +29762,9 @@
       </c>
       <c r="P504" t="n">
         <v>269</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>348777356</v>
       </c>
     </row>
     <row r="505" ht="19" customHeight="1">
@@ -28298,6 +29810,9 @@
       <c r="P505" t="n">
         <v>155</v>
       </c>
+      <c r="Q505" t="n">
+        <v>353036232</v>
+      </c>
     </row>
     <row r="506" ht="19" customHeight="1">
       <c r="A506" s="1" t="n">
@@ -28350,6 +29865,9 @@
       <c r="P506" t="n">
         <v>107</v>
       </c>
+      <c r="Q506" t="n">
+        <v>383791808</v>
+      </c>
     </row>
     <row r="507" ht="19" customHeight="1">
       <c r="A507" s="1" t="n">
@@ -28402,6 +29920,9 @@
       <c r="P507" t="n">
         <v>107</v>
       </c>
+      <c r="Q507" t="n">
+        <v>350895240</v>
+      </c>
     </row>
     <row r="508" ht="19" customHeight="1">
       <c r="A508" s="1" t="n">
@@ -28456,6 +29977,9 @@
       <c r="P508" t="n">
         <v>136</v>
       </c>
+      <c r="Q508" t="n">
+        <v>351383918</v>
+      </c>
     </row>
     <row r="509" ht="19" customHeight="1">
       <c r="A509" s="1" t="n">
@@ -28510,6 +30034,9 @@
       <c r="P509" t="n">
         <v>116</v>
       </c>
+      <c r="Q509" t="n">
+        <v>385480320</v>
+      </c>
     </row>
     <row r="510" ht="19" customHeight="1">
       <c r="A510" s="1" t="n">
@@ -28570,6 +30097,9 @@
       <c r="P510" t="n">
         <v>138</v>
       </c>
+      <c r="Q510" t="n">
+        <v>348590986</v>
+      </c>
     </row>
     <row r="511" ht="19" customHeight="1">
       <c r="A511" s="1" t="n">
@@ -28621,6 +30151,9 @@
       </c>
       <c r="P511" t="n">
         <v>160</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>357186846</v>
       </c>
     </row>
     <row r="512" ht="19" customHeight="1">
@@ -28676,6 +30209,9 @@
       <c r="P512" t="n">
         <v>265</v>
       </c>
+      <c r="Q512" t="n">
+        <v>383828310</v>
+      </c>
     </row>
     <row r="513" ht="19" customHeight="1">
       <c r="A513" s="1" t="n">
@@ -28731,6 +30267,9 @@
       </c>
       <c r="P513" t="n">
         <v>144</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>352042890</v>
       </c>
     </row>
     <row r="514" ht="19" customHeight="1">
@@ -28776,6 +30315,9 @@
       <c r="P514" t="n">
         <v>129</v>
       </c>
+      <c r="Q514" t="n">
+        <v>359262232</v>
+      </c>
     </row>
     <row r="515" ht="19" customHeight="1">
       <c r="A515" s="1" t="n">
@@ -28830,6 +30372,9 @@
       <c r="P515" t="n">
         <v>190</v>
       </c>
+      <c r="Q515" t="n">
+        <v>398851460</v>
+      </c>
     </row>
     <row r="516" ht="19" customHeight="1">
       <c r="A516" s="1" t="n">
@@ -28882,6 +30427,9 @@
       <c r="P516" t="n">
         <v>67</v>
       </c>
+      <c r="Q516" t="n">
+        <v>364932922</v>
+      </c>
     </row>
     <row r="517" ht="19" customHeight="1">
       <c r="A517" s="1" t="n">
@@ -28934,6 +30482,9 @@
       <c r="P517" t="n">
         <v>67</v>
       </c>
+      <c r="Q517" t="n">
+        <v>366420958</v>
+      </c>
     </row>
     <row r="518" ht="19" customHeight="1">
       <c r="A518" s="1" t="n">
@@ -28985,6 +30536,9 @@
       </c>
       <c r="P518" t="n">
         <v>118</v>
+      </c>
+      <c r="Q518" t="n">
+        <v>398243350</v>
       </c>
     </row>
     <row r="519" ht="19" customHeight="1">
@@ -29030,6 +30584,9 @@
       <c r="P519" t="n">
         <v>122</v>
       </c>
+      <c r="Q519" t="n">
+        <v>376311750</v>
+      </c>
     </row>
     <row r="520" ht="19" customHeight="1">
       <c r="A520" s="1" t="n">
@@ -29085,6 +30642,9 @@
       </c>
       <c r="P520" t="n">
         <v>87</v>
+      </c>
+      <c r="Q520" t="n">
+        <v>306235982</v>
       </c>
     </row>
     <row r="521" ht="19" customHeight="1">
@@ -29134,6 +30694,9 @@
       <c r="P521" t="n">
         <v>604</v>
       </c>
+      <c r="Q521" t="n">
+        <v>330722178</v>
+      </c>
     </row>
     <row r="522" ht="19" customHeight="1">
       <c r="A522" s="1" t="n">
@@ -29187,6 +30750,9 @@
       </c>
       <c r="P522" t="n">
         <v>62</v>
+      </c>
+      <c r="Q522" t="n">
+        <v>363037044</v>
       </c>
     </row>
     <row r="523" ht="19" customHeight="1">
@@ -29232,6 +30798,9 @@
       <c r="P523" t="n">
         <v>177</v>
       </c>
+      <c r="Q523" t="n">
+        <v>389301568</v>
+      </c>
     </row>
     <row r="524" ht="19" customHeight="1">
       <c r="A524" s="1" t="n">
@@ -29288,6 +30857,9 @@
       <c r="P524" t="n">
         <v>80</v>
       </c>
+      <c r="Q524" t="n">
+        <v>357347556</v>
+      </c>
     </row>
     <row r="525" ht="19" customHeight="1">
       <c r="A525" s="1" t="n">
@@ -29340,6 +30912,9 @@
       <c r="P525" t="n">
         <v>564</v>
       </c>
+      <c r="Q525" t="n">
+        <v>364080712</v>
+      </c>
     </row>
     <row r="526" ht="19" customHeight="1">
       <c r="A526" s="1" t="n">
@@ -29400,6 +30975,9 @@
       <c r="P526" t="n">
         <v>47</v>
       </c>
+      <c r="Q526" t="n">
+        <v>385873150</v>
+      </c>
     </row>
     <row r="527" ht="19" customHeight="1">
       <c r="A527" s="1" t="n">
@@ -29455,6 +31033,9 @@
       </c>
       <c r="P527" t="n">
         <v>174</v>
+      </c>
+      <c r="Q527" t="n">
+        <v>354466956</v>
       </c>
     </row>
     <row r="528" ht="19" customHeight="1">
@@ -29508,6 +31089,9 @@
       <c r="P528" t="n">
         <v>151</v>
       </c>
+      <c r="Q528" t="n">
+        <v>363694232</v>
+      </c>
     </row>
     <row r="529" ht="19" customHeight="1">
       <c r="A529" s="1" t="n">
@@ -29560,6 +31144,9 @@
       <c r="P529" t="n">
         <v>166</v>
       </c>
+      <c r="Q529" t="n">
+        <v>386747886</v>
+      </c>
     </row>
     <row r="530" ht="19" customHeight="1">
       <c r="A530" s="1" t="n">
@@ -29616,6 +31203,9 @@
       <c r="P530" t="n">
         <v>154</v>
       </c>
+      <c r="Q530" t="n">
+        <v>354991248</v>
+      </c>
     </row>
     <row r="531" ht="19" customHeight="1">
       <c r="A531" s="1" t="n">
@@ -29672,6 +31262,9 @@
       <c r="P531" t="n">
         <v>248</v>
       </c>
+      <c r="Q531" t="n">
+        <v>358732158</v>
+      </c>
     </row>
     <row r="532" ht="19" customHeight="1">
       <c r="A532" s="1" t="n">
@@ -29734,6 +31327,9 @@
       <c r="P532" t="n">
         <v>100</v>
       </c>
+      <c r="Q532" t="n">
+        <v>399441700</v>
+      </c>
     </row>
     <row r="533" ht="19" customHeight="1">
       <c r="A533" s="1" t="n">
@@ -29785,6 +31381,9 @@
       </c>
       <c r="P533" t="n">
         <v>128</v>
+      </c>
+      <c r="Q533" t="n">
+        <v>360915142</v>
       </c>
     </row>
     <row r="534" ht="19" customHeight="1">
@@ -29838,6 +31437,9 @@
       <c r="P534" t="n">
         <v>142</v>
       </c>
+      <c r="Q534" t="n">
+        <v>371066844</v>
+      </c>
     </row>
     <row r="535" ht="19" customHeight="1">
       <c r="A535" s="1" t="n">
@@ -29893,6 +31495,9 @@
       </c>
       <c r="P535" t="n">
         <v>194</v>
+      </c>
+      <c r="Q535" t="n">
+        <v>403899176</v>
       </c>
     </row>
     <row r="536" ht="19" customHeight="1">
@@ -29934,6 +31539,9 @@
       <c r="P536" t="n">
         <v>183</v>
       </c>
+      <c r="Q536" t="n">
+        <v>377466594</v>
+      </c>
     </row>
     <row r="537" ht="19" customHeight="1">
       <c r="A537" s="1" t="n">
@@ -29993,6 +31601,9 @@
       </c>
       <c r="P537" t="n">
         <v>98</v>
+      </c>
+      <c r="Q537" t="n">
+        <v>385122072</v>
       </c>
     </row>
     <row r="538" ht="19" customHeight="1">
@@ -30034,6 +31645,9 @@
       <c r="P538" t="n">
         <v>135</v>
       </c>
+      <c r="Q538" t="n">
+        <v>409235610</v>
+      </c>
     </row>
     <row r="539" ht="19" customHeight="1">
       <c r="A539" s="1" t="n">
@@ -30082,6 +31696,9 @@
       <c r="P539" t="n">
         <v>148</v>
       </c>
+      <c r="Q539" t="n">
+        <v>363914948</v>
+      </c>
     </row>
     <row r="540" ht="19" customHeight="1">
       <c r="A540" s="1" t="n">
@@ -30134,6 +31751,9 @@
       <c r="P540" t="n">
         <v>123</v>
       </c>
+      <c r="Q540" t="n">
+        <v>374640566</v>
+      </c>
     </row>
     <row r="541" ht="19" customHeight="1">
       <c r="A541" s="1" t="n">
@@ -30196,6 +31816,9 @@
       <c r="P541" t="n">
         <v>104</v>
       </c>
+      <c r="Q541" t="n">
+        <v>400247838</v>
+      </c>
     </row>
     <row r="542" ht="19" customHeight="1">
       <c r="A542" s="8" t="n">
@@ -30247,6 +31870,9 @@
       </c>
       <c r="P542" t="n">
         <v>101</v>
+      </c>
+      <c r="Q542" t="n">
+        <v>361034006</v>
       </c>
     </row>
     <row r="543" ht="19" customHeight="1">
@@ -30294,6 +31920,9 @@
       <c r="P543" t="n">
         <v>114</v>
       </c>
+      <c r="Q543" t="n">
+        <v>364942202</v>
+      </c>
     </row>
     <row r="544" ht="19" customHeight="1">
       <c r="A544" s="14" t="n">
@@ -30355,6 +31984,9 @@
       </c>
       <c r="P544" t="n">
         <v>78</v>
+      </c>
+      <c r="Q544" t="n">
+        <v>396317254</v>
       </c>
     </row>
     <row r="545" ht="19" customHeight="1">
@@ -30404,6 +32036,9 @@
       <c r="P545" t="n">
         <v>142</v>
       </c>
+      <c r="Q545" t="n">
+        <v>358264332</v>
+      </c>
     </row>
     <row r="546" ht="19" customHeight="1">
       <c r="A546" s="8" t="n">
@@ -30460,6 +32095,9 @@
       <c r="P546" t="n">
         <v>126</v>
       </c>
+      <c r="Q546" t="n">
+        <v>362437084</v>
+      </c>
     </row>
     <row r="547" ht="19" customHeight="1">
       <c r="A547" s="5" t="n">
@@ -30522,6 +32160,9 @@
       <c r="P547" t="n">
         <v>112</v>
       </c>
+      <c r="Q547" t="n">
+        <v>390055596</v>
+      </c>
     </row>
     <row r="548" ht="19" customHeight="1">
       <c r="A548" s="1" t="n">
@@ -30576,6 +32217,9 @@
       <c r="P548" t="n">
         <v>79</v>
       </c>
+      <c r="Q548" t="n">
+        <v>353205678</v>
+      </c>
     </row>
     <row r="549" ht="19" customHeight="1">
       <c r="A549" s="1" t="n">
@@ -30637,6 +32281,9 @@
       </c>
       <c r="P549" t="n">
         <v>81</v>
+      </c>
+      <c r="Q549" t="n">
+        <v>357498010</v>
       </c>
     </row>
     <row r="550" ht="19" customHeight="1">
@@ -30682,6 +32329,9 @@
       <c r="P550" t="n">
         <v>180</v>
       </c>
+      <c r="Q550" t="n">
+        <v>379272340</v>
+      </c>
     </row>
     <row r="551" ht="19" customHeight="1">
       <c r="A551" s="1" t="n">
@@ -30741,6 +32391,9 @@
       </c>
       <c r="P551" t="n">
         <v>89</v>
+      </c>
+      <c r="Q551" t="n">
+        <v>356306424</v>
       </c>
     </row>
     <row r="552" ht="19" customHeight="1">
@@ -30786,6 +32439,9 @@
       <c r="P552" t="n">
         <v>192</v>
       </c>
+      <c r="Q552" t="n">
+        <v>365633358</v>
+      </c>
     </row>
     <row r="553" ht="19" customHeight="1">
       <c r="A553" s="5" t="n">
@@ -30837,6 +32493,9 @@
       </c>
       <c r="P553" t="n">
         <v>118</v>
+      </c>
+      <c r="Q553" t="n">
+        <v>392695744</v>
       </c>
     </row>
     <row r="554" ht="19" customHeight="1">
@@ -30892,6 +32551,9 @@
       <c r="P554" t="n">
         <v>139</v>
       </c>
+      <c r="Q554" t="n">
+        <v>353582370</v>
+      </c>
     </row>
     <row r="555" ht="19" customHeight="1">
       <c r="A555" s="5" t="n">
@@ -30953,6 +32615,9 @@
       </c>
       <c r="P555" t="n">
         <v>130</v>
+      </c>
+      <c r="Q555" t="n">
+        <v>355328424</v>
       </c>
     </row>
     <row r="556" ht="19" customHeight="1">
@@ -30998,6 +32663,9 @@
       <c r="P556" t="n">
         <v>208</v>
       </c>
+      <c r="Q556" t="n">
+        <v>388447078</v>
+      </c>
     </row>
     <row r="557" ht="19" customHeight="1">
       <c r="A557" s="5" t="n">
@@ -31054,6 +32722,9 @@
       <c r="P557" t="n">
         <v>125</v>
       </c>
+      <c r="Q557" t="n">
+        <v>369383528</v>
+      </c>
     </row>
     <row r="558" ht="19" customHeight="1">
       <c r="A558" s="1" t="n">
@@ -31109,6 +32780,9 @@
       </c>
       <c r="P558" t="n">
         <v>154</v>
+      </c>
+      <c r="Q558" t="n">
+        <v>348080190</v>
       </c>
     </row>
     <row r="559" ht="19" customHeight="1">
@@ -31150,6 +32824,9 @@
       <c r="P559" t="n">
         <v>119</v>
       </c>
+      <c r="Q559" t="n">
+        <v>377330734</v>
+      </c>
     </row>
     <row r="560" ht="19" customHeight="1">
       <c r="A560" s="1" t="n">
@@ -31204,6 +32881,9 @@
       <c r="P560" t="n">
         <v>130</v>
       </c>
+      <c r="Q560" t="n">
+        <v>352267432</v>
+      </c>
     </row>
     <row r="561" ht="19" customHeight="1">
       <c r="A561" s="1" t="n">
@@ -31263,6 +32943,9 @@
       </c>
       <c r="P561" t="n">
         <v>128</v>
+      </c>
+      <c r="Q561" t="n">
+        <v>361167416</v>
       </c>
     </row>
     <row r="562" ht="19" customHeight="1">
@@ -31312,6 +32995,9 @@
       <c r="P562" t="n">
         <v>66</v>
       </c>
+      <c r="Q562" t="n">
+        <v>387903486</v>
+      </c>
     </row>
     <row r="563" ht="19" customHeight="1">
       <c r="A563" s="1" t="n">
@@ -31372,6 +33058,9 @@
       <c r="P563" t="n">
         <v>147</v>
       </c>
+      <c r="Q563" t="n">
+        <v>352228044</v>
+      </c>
     </row>
     <row r="564" ht="19" customHeight="1">
       <c r="A564" s="1" t="n">
@@ -31428,6 +33117,9 @@
       <c r="P564" t="n">
         <v>149</v>
       </c>
+      <c r="Q564" t="n">
+        <v>360236814</v>
+      </c>
     </row>
     <row r="565" ht="19" customHeight="1">
       <c r="A565" s="1" t="n">
@@ -31482,6 +33174,9 @@
       <c r="P565" t="n">
         <v>107</v>
       </c>
+      <c r="Q565" t="n">
+        <v>388652642</v>
+      </c>
     </row>
     <row r="566" ht="19" customHeight="1">
       <c r="A566" s="1" t="n">
@@ -31534,6 +33229,9 @@
       <c r="P566" t="n">
         <v>276</v>
       </c>
+      <c r="Q566" t="n">
+        <v>347159860</v>
+      </c>
     </row>
     <row r="567" ht="19" customHeight="1">
       <c r="A567" s="1" t="n">
@@ -31594,6 +33292,9 @@
       <c r="P567" t="n">
         <v>223</v>
       </c>
+      <c r="Q567" t="n">
+        <v>358486254</v>
+      </c>
     </row>
     <row r="568" ht="19" customHeight="1">
       <c r="A568" s="1" t="n">
@@ -31653,6 +33354,9 @@
       </c>
       <c r="P568" t="n">
         <v>77</v>
+      </c>
+      <c r="Q568" t="n">
+        <v>394441490</v>
       </c>
     </row>
     <row r="569" ht="19" customHeight="1">
@@ -31700,6 +33404,9 @@
       <c r="P569" t="n">
         <v>65</v>
       </c>
+      <c r="Q569" t="n">
+        <v>358422924</v>
+      </c>
     </row>
     <row r="570" ht="19" customHeight="1">
       <c r="A570" s="1" t="n">
@@ -31754,6 +33461,9 @@
       <c r="P570" t="n">
         <v>103</v>
       </c>
+      <c r="Q570" t="n">
+        <v>380549690</v>
+      </c>
     </row>
     <row r="571" ht="19" customHeight="1">
       <c r="A571" s="1" t="n">
@@ -31806,6 +33516,9 @@
       <c r="P571" t="n">
         <v>201</v>
       </c>
+      <c r="Q571" t="n">
+        <v>386492580</v>
+      </c>
     </row>
     <row r="572" ht="19" customHeight="1">
       <c r="A572" s="1" t="n">
@@ -31860,6 +33573,9 @@
       <c r="P572" t="n">
         <v>148</v>
       </c>
+      <c r="Q572" t="n">
+        <v>359738534</v>
+      </c>
     </row>
     <row r="573" ht="19" customHeight="1">
       <c r="A573" s="1" t="n">
@@ -31921,6 +33637,9 @@
       </c>
       <c r="P573" t="n">
         <v>247</v>
+      </c>
+      <c r="Q573" t="n">
+        <v>364669398</v>
       </c>
     </row>
     <row r="574" ht="19" customHeight="1">
@@ -31966,6 +33685,9 @@
       <c r="P574" t="n">
         <v>130</v>
       </c>
+      <c r="Q574" t="n">
+        <v>387896530</v>
+      </c>
     </row>
     <row r="575" ht="19" customHeight="1">
       <c r="A575" s="1" t="n">
@@ -32014,6 +33736,9 @@
       <c r="P575" t="n">
         <v>82</v>
       </c>
+      <c r="Q575" t="n">
+        <v>365733450</v>
+      </c>
     </row>
     <row r="576" ht="19" customHeight="1">
       <c r="A576" s="1" t="n">
@@ -32076,6 +33801,9 @@
       <c r="P576" t="n">
         <v>220</v>
       </c>
+      <c r="Q576" t="n">
+        <v>428387634</v>
+      </c>
     </row>
     <row r="577" ht="19" customHeight="1">
       <c r="A577" s="1" t="n">
@@ -32136,6 +33864,9 @@
       <c r="P577" t="n">
         <v>64</v>
       </c>
+      <c r="Q577" t="n">
+        <v>381989060</v>
+      </c>
     </row>
     <row r="578" ht="19" customHeight="1">
       <c r="A578" s="1" t="n">
@@ -32198,6 +33929,9 @@
       <c r="P578" t="n">
         <v>113</v>
       </c>
+      <c r="Q578" t="n">
+        <v>351619166</v>
+      </c>
     </row>
     <row r="579" ht="19" customHeight="1">
       <c r="A579" s="1" t="n">
@@ -32250,6 +33984,9 @@
       <c r="P579" t="n">
         <v>152</v>
       </c>
+      <c r="Q579" t="n">
+        <v>380507698</v>
+      </c>
     </row>
     <row r="580" ht="19" customHeight="1">
       <c r="A580" s="1" t="n">
@@ -32302,6 +34039,9 @@
       <c r="P580" t="n">
         <v>133</v>
       </c>
+      <c r="Q580" t="n">
+        <v>361967792</v>
+      </c>
     </row>
     <row r="581" ht="19" customHeight="1">
       <c r="A581" s="1" t="n">
@@ -32364,6 +34104,9 @@
       <c r="P581" t="n">
         <v>79</v>
       </c>
+      <c r="Q581" t="n">
+        <v>370443834</v>
+      </c>
     </row>
     <row r="582" ht="19" customHeight="1">
       <c r="A582" s="1" t="n">
@@ -32426,6 +34169,9 @@
       <c r="P582" t="n">
         <v>184</v>
       </c>
+      <c r="Q582" t="n">
+        <v>404403816</v>
+      </c>
     </row>
     <row r="583" ht="19" customHeight="1">
       <c r="A583" s="1" t="n">
@@ -32477,6 +34223,9 @@
       </c>
       <c r="P583" t="n">
         <v>168</v>
+      </c>
+      <c r="Q583" t="n">
+        <v>377828982</v>
       </c>
     </row>
     <row r="584" ht="19" customHeight="1">
@@ -32531,6 +34280,9 @@
       </c>
       <c r="P584" t="n">
         <v>131</v>
+      </c>
+      <c r="Q584" t="n">
+        <v>397777968</v>
       </c>
     </row>
     <row r="585" ht="19" customHeight="1">
@@ -32578,6 +34330,9 @@
       <c r="P585" t="n">
         <v>251</v>
       </c>
+      <c r="Q585" t="n">
+        <v>425241582</v>
+      </c>
     </row>
     <row r="586" ht="19" customHeight="1">
       <c r="A586" s="1" t="n">
@@ -32632,6 +34387,9 @@
       <c r="P586" t="n">
         <v>106</v>
       </c>
+      <c r="Q586" t="n">
+        <v>390925844</v>
+      </c>
     </row>
     <row r="587" ht="19" customHeight="1">
       <c r="A587" s="1" t="n">
@@ -32694,6 +34452,9 @@
       <c r="P587" t="n">
         <v>86</v>
       </c>
+      <c r="Q587" t="n">
+        <v>401991268</v>
+      </c>
     </row>
     <row r="588" ht="19" customHeight="1">
       <c r="A588" s="1" t="n">
@@ -32754,6 +34515,9 @@
       <c r="P588" t="n">
         <v>99</v>
       </c>
+      <c r="Q588" t="n">
+        <v>430685136</v>
+      </c>
     </row>
     <row r="589" ht="19" customHeight="1">
       <c r="A589" s="1" t="n">
@@ -32808,6 +34572,9 @@
       <c r="P589" t="n">
         <v>120</v>
       </c>
+      <c r="Q589" t="n">
+        <v>392702390</v>
+      </c>
     </row>
     <row r="590" ht="19" customHeight="1">
       <c r="A590" s="1" t="n">
@@ -32868,6 +34635,9 @@
       <c r="P590" t="n">
         <v>161</v>
       </c>
+      <c r="Q590" t="n">
+        <v>397739574</v>
+      </c>
     </row>
     <row r="591" ht="19" customHeight="1">
       <c r="A591" s="1" t="n">
@@ -32930,6 +34700,9 @@
       <c r="P591" t="n">
         <v>183</v>
       </c>
+      <c r="Q591" t="n">
+        <v>425726210</v>
+      </c>
     </row>
     <row r="592" ht="19" customHeight="1">
       <c r="A592" s="1" t="n">
@@ -32986,6 +34759,9 @@
       <c r="P592" t="n">
         <v>268</v>
       </c>
+      <c r="Q592" t="n">
+        <v>389527084</v>
+      </c>
     </row>
     <row r="593" ht="19" customHeight="1">
       <c r="A593" s="1" t="n">
@@ -33040,6 +34816,9 @@
       <c r="P593" t="n">
         <v>177</v>
       </c>
+      <c r="Q593" t="n">
+        <v>398552206</v>
+      </c>
     </row>
     <row r="594" ht="19" customHeight="1">
       <c r="A594" s="1" t="n">
@@ -33092,6 +34871,9 @@
       <c r="P594" t="n">
         <v>171</v>
       </c>
+      <c r="Q594" t="n">
+        <v>398672542</v>
+      </c>
     </row>
     <row r="595" ht="19" customHeight="1">
       <c r="A595" s="1" t="n">
@@ -33152,6 +34934,9 @@
       <c r="P595" t="n">
         <v>139</v>
       </c>
+      <c r="Q595" t="n">
+        <v>382309000</v>
+      </c>
     </row>
     <row r="596" ht="19" customHeight="1">
       <c r="A596" s="1" t="n">
@@ -33212,6 +34997,9 @@
       <c r="P596" t="n">
         <v>173</v>
       </c>
+      <c r="Q596" t="n">
+        <v>393444014</v>
+      </c>
     </row>
     <row r="597" ht="19" customHeight="1">
       <c r="A597" s="1" t="n">
@@ -33267,6 +35055,9 @@
       </c>
       <c r="P597" t="n">
         <v>222</v>
+      </c>
+      <c r="Q597" t="n">
+        <v>421923472</v>
       </c>
     </row>
     <row r="598" ht="19" customHeight="1">
@@ -33308,6 +35099,9 @@
       <c r="P598" t="n">
         <v>171</v>
       </c>
+      <c r="Q598" t="n">
+        <v>396284492</v>
+      </c>
     </row>
     <row r="599" ht="19" customHeight="1">
       <c r="A599" s="1" t="n">
@@ -33361,6 +35155,9 @@
       </c>
       <c r="P599" t="n">
         <v>350</v>
+      </c>
+      <c r="Q599" t="n">
+        <v>400801534</v>
       </c>
     </row>
     <row r="600" ht="19" customHeight="1">
@@ -33410,6 +35207,9 @@
       <c r="P600" t="n">
         <v>262</v>
       </c>
+      <c r="Q600" t="n">
+        <v>423102342</v>
+      </c>
     </row>
     <row r="601" ht="19" customHeight="1">
       <c r="A601" s="1" t="n">
@@ -33470,6 +35270,9 @@
       <c r="P601" t="n">
         <v>114</v>
       </c>
+      <c r="Q601" t="n">
+        <v>395282770</v>
+      </c>
     </row>
     <row r="602" ht="19" customHeight="1">
       <c r="A602" s="1" t="n">
@@ -33523,6 +35326,9 @@
       </c>
       <c r="P602" t="n">
         <v>131</v>
+      </c>
+      <c r="Q602" t="n">
+        <v>395637026</v>
       </c>
     </row>
     <row r="603" ht="19" customHeight="1">
@@ -33576,6 +35382,9 @@
       <c r="P603" t="n">
         <v>114</v>
       </c>
+      <c r="Q603" t="n">
+        <v>425615512</v>
+      </c>
     </row>
     <row r="604" ht="19" customHeight="1">
       <c r="A604" s="1" t="n">
@@ -33628,6 +35437,9 @@
       <c r="P604" t="n">
         <v>269</v>
       </c>
+      <c r="Q604" t="n">
+        <v>383992530</v>
+      </c>
     </row>
     <row r="605" ht="19" customHeight="1">
       <c r="A605" s="1" t="n">
@@ -33680,6 +35492,9 @@
       <c r="P605" t="n">
         <v>128</v>
       </c>
+      <c r="Q605" t="n">
+        <v>381163108</v>
+      </c>
     </row>
     <row r="606" ht="19" customHeight="1">
       <c r="A606" s="1" t="n">
@@ -33741,6 +35556,9 @@
       </c>
       <c r="P606" t="n">
         <v>112</v>
+      </c>
+      <c r="Q606" t="n">
+        <v>378548054</v>
       </c>
     </row>
     <row r="607" ht="19" customHeight="1">
@@ -33790,6 +35608,9 @@
       <c r="P607" t="n">
         <v>87</v>
       </c>
+      <c r="Q607" t="n">
+        <v>368215788</v>
+      </c>
     </row>
     <row r="608" ht="19" customHeight="1">
       <c r="A608" s="1" t="n">
@@ -33851,6 +35672,9 @@
       </c>
       <c r="P608" t="n">
         <v>189</v>
+      </c>
+      <c r="Q608" t="n">
+        <v>386809756</v>
       </c>
     </row>
     <row r="609" ht="19" customHeight="1">
@@ -33900,6 +35724,9 @@
       <c r="P609" t="n">
         <v>257</v>
       </c>
+      <c r="Q609" t="n">
+        <v>417267288</v>
+      </c>
     </row>
     <row r="610" ht="19" customHeight="1">
       <c r="A610" s="1" t="n">
@@ -33962,6 +35789,9 @@
       <c r="P610" t="n">
         <v>136</v>
       </c>
+      <c r="Q610" t="n">
+        <v>395029142</v>
+      </c>
     </row>
     <row r="611" ht="19" customHeight="1">
       <c r="A611" s="1" t="n">
@@ -34022,6 +35852,9 @@
       <c r="P611" t="n">
         <v>67</v>
       </c>
+      <c r="Q611" t="n">
+        <v>391858874</v>
+      </c>
     </row>
     <row r="612" ht="19" customHeight="1">
       <c r="A612" s="1" t="n">
@@ -34084,6 +35917,9 @@
       <c r="P612" t="n">
         <v>155</v>
       </c>
+      <c r="Q612" t="n">
+        <v>422769486</v>
+      </c>
     </row>
     <row r="613" ht="19" customHeight="1">
       <c r="A613" s="1" t="n">
@@ -34144,6 +35980,9 @@
       <c r="P613" t="n">
         <v>86</v>
       </c>
+      <c r="Q613" t="n">
+        <v>391304582</v>
+      </c>
     </row>
     <row r="614" ht="19" customHeight="1">
       <c r="A614" s="1" t="n">
@@ -34198,6 +36037,9 @@
       <c r="P614" t="n">
         <v>109</v>
       </c>
+      <c r="Q614" t="n">
+        <v>397400020</v>
+      </c>
     </row>
     <row r="615" ht="19" customHeight="1">
       <c r="A615" s="1" t="n">
@@ -34260,6 +36102,9 @@
       <c r="P615" t="n">
         <v>154</v>
       </c>
+      <c r="Q615" t="n">
+        <v>425121686</v>
+      </c>
     </row>
     <row r="616" ht="19" customHeight="1">
       <c r="A616" s="1" t="n">
@@ -34322,6 +36167,9 @@
       <c r="P616" t="n">
         <v>138</v>
       </c>
+      <c r="Q616" t="n">
+        <v>392773558</v>
+      </c>
     </row>
     <row r="617" ht="19" customHeight="1">
       <c r="A617" s="1" t="n">
@@ -34382,6 +36230,9 @@
       <c r="P617" t="n">
         <v>226</v>
       </c>
+      <c r="Q617" t="n">
+        <v>398771788</v>
+      </c>
     </row>
     <row r="618" ht="19" customHeight="1">
       <c r="A618" s="1" t="n">
@@ -34438,6 +36289,9 @@
       <c r="P618" t="n">
         <v>135</v>
       </c>
+      <c r="Q618" t="n">
+        <v>429422172</v>
+      </c>
     </row>
     <row r="619" ht="19" customHeight="1">
       <c r="A619" s="1" t="n">
@@ -34500,6 +36354,9 @@
       <c r="P619" t="n">
         <v>139</v>
       </c>
+      <c r="Q619" t="n">
+        <v>402189304</v>
+      </c>
     </row>
     <row r="620" ht="19" customHeight="1">
       <c r="A620" s="1" t="n">
@@ -34561,6 +36418,9 @@
       </c>
       <c r="P620" t="n">
         <v>117</v>
+      </c>
+      <c r="Q620" t="n">
+        <v>393294950</v>
       </c>
     </row>
     <row r="621" ht="19" customHeight="1">
@@ -34610,6 +36470,9 @@
       <c r="P621" t="n">
         <v>168</v>
       </c>
+      <c r="Q621" t="n">
+        <v>427210484</v>
+      </c>
     </row>
     <row r="622" ht="19" customHeight="1">
       <c r="A622" s="1" t="n">
@@ -34658,6 +36521,9 @@
       <c r="P622" t="n">
         <v>190</v>
       </c>
+      <c r="Q622" t="n">
+        <v>386314046</v>
+      </c>
     </row>
     <row r="623" ht="19" customHeight="1">
       <c r="A623" s="1" t="n">
@@ -34718,6 +36584,9 @@
       <c r="P623" t="n">
         <v>126</v>
       </c>
+      <c r="Q623" t="n">
+        <v>392786646</v>
+      </c>
     </row>
     <row r="624" ht="19" customHeight="1">
       <c r="A624" s="1" t="n">
@@ -34777,6 +36646,9 @@
       </c>
       <c r="P624" t="n">
         <v>89</v>
+      </c>
+      <c r="Q624" t="n">
+        <v>414869642</v>
       </c>
     </row>
   </sheetData>
